--- a/evaluace.xlsx
+++ b/evaluace.xlsx
@@ -1747,12 +1747,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkxMjUxNzAxMDtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkxMjUxNzAxNjtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Smlouva evaluace publicity IROP vč. příloh.pdf</t>
+          <t>Vyhodnocení komunikačních aktivit IROP_Zaverecna_Zprava.pdf</t>
         </is>
       </c>
     </row>

--- a/evaluace.xlsx
+++ b/evaluace.xlsx
@@ -1389,27 +1389,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OP ZP</t>
+          <t>IROP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05.006.01</t>
+          <t>06.010.01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OP ZP  •  Provedení hodnocení vlivu OPŽP na životní prostředí v období 2021-2027 (SEA)</t>
+          <t>IROP  •  Posouzení vlivu IROP II. na životní prostředí pro programové období 2021-2027</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Provedení hodnocení vlivu OPŽP na životní prostředí v období 2021-2027 (SEA)</t>
+          <t>Posouzení vlivu IROP II. na životní prostředí pro programové období 2021-2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Provedení hodnocení vlivu OPŽP na životní prostředí v období 2021-2027 (SEA)</t>
+          <t>Posouzení vlivu IROP II. na životní prostředí pro programové období 2021-2027</t>
         </is>
       </c>
       <c r="F12" s="2">
@@ -1422,105 +1422,15 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Cílem projektu je provedení posouzení vlivu OPŽP 2021-2027 na životní prostředí v souladu s platnými právními předpisy.</t>
+          <t>Posouzení vlivu IROP II. na životní prostředí pro programové období 2021-2027</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Cílem projektu je provedení posouzení vlivu OPŽP 2021-2027 na životní prostředí v souladu s platnými právními předpisy.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Jiná</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>horizontální témata</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>ad-hoc</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Strategická, Tematická</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODgwMjUyMzAxO1ByaWxvaGFETVM7RmFsc2U=</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Vyhodnocení SEA OPŽP 03082021.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>IROP</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>06.010.01</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>IROP  •  Posouzení vlivu IROP II. na životní prostředí pro programové období 2021-2027</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Posouzení vlivu IROP II. na životní prostředí pro programové období 2021-2027</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Posouzení vlivu IROP II. na životní prostředí pro programové období 2021-2027</t>
-        </is>
-      </c>
-      <c r="F13" s="2">
-        <v>45291</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Posouzení vlivu IROP II. na životní prostředí pro programové období 2021-2027</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
           <t>Předmětem plnění je vyhodnocení vlivů IROP v programovém období 2021-2027 na životní prostředí a veřejné zdraví dle zákona č. 100/2001 Sb., o posuzování vlivů na životní prostředí, ve znění pozdějších předpisů, známé také jako SEA (Strategic Environmental Assessment).</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Jednotlivé priority, z nich plynoucí specifické cíle a celkové strategické směřování návrhu IROP jsou v souladu s relevantními cíli strategických dokumentů uvedených ve vyhodnocení SEA (konkrétně v kapitole 1), které mají vztah k životnímu prostředí a veřejnému zdraví.
 Potenciální negativní vlivy plynoucí z implementace Priority 1 nebyly identifikovány. 
@@ -1530,6 +1440,96 @@
 Podpora udržitelného a integrovaného rozvoje městských a venkovských oblastí a místních iniciativ bude v rámci Priority 5 realizována prostřednictvím komunitně vedeného místního rozvoje (CLLD), jehož typová a tematická variabilita je značná dle potřeb daných regionů. Obecně lze předpokládat, že takovýto typ rozvoje bude prováděn pro odstraňování problémů či bariér rozvoje v daných mikroregionech, a že by měl přispět k pozitivní stimulaci stavu životního prostředí. Nicméně mohou být do něj zahrnuty i takové aktivity, které mohou životní prostředí ovlivňovat potenciálně negativně. Příkladem lze potenciál možného mírného negativního ovlivnění identifikovat u podpory dopravní infrastruktury a infrastruktury pro cyklistickou dopravu či veřejné infrastruktury udržitelného cestovního ruchu.</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Jiná</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>ex-ante</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Strategická, Operativní/procesní</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODU5NzUxMjA3O1ByaWxvaGFETVM7RmFsc2U=</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>01 SEA_IROP_2021_2027_Vyhodnoceni.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>OP Z</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>03.044.01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>OP Z  •  Evaluace výsledků výzvy Podpora programu Housing First (Bydlení především)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Evaluace výsledků výzvy Podpora programu Housing First (Bydlení především)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Vyhodnocení dotazníku pro evaluaci dopadů programu HF pro řešení bytové nouze</t>
+        </is>
+      </c>
+      <c r="F13" s="2">
+        <v>45289</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Vyhodnotit přínosy projektů z výzvy na podporu pilotního rozšíření konceptu Housing First / Bydlení především pro cílové skupiny.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Od června 2019 probíhá příprava podkladů (scénářů dotazníků) pro interní sběr dat u příjemců podpory a cílové skupiny. Scénář dotazníku pro cílové skupiny před nastěhováním do sociálního bydlení byl v září 2019 opilotován a od října 2019 začíná plošný sběr dat. Během 2020 dokončeny verze dotazníku po 12 měsících / 24 měsících od zabydlení domácností.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>85 % domácností bydlelo v bytě poskytnutém v projektu alespoň 1 rok. U 89 % zabydlených se zvýšila spokojenost s bydlením. U 74 % domácností s dětmi došlo ke zkvalitnění prostoru pro děti. U 65 % zabydlených se zlepšil psychický stav (měřeno dle Kesslerovy škály psychosociální tísně). U 57 % se zvýšila spokojenost se životem (rok po zabydlení uvedlo 87 % dotázaných, že jsou spokojeni se životem).</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Ano</t>
@@ -1547,58 +1547,58 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Jiná</t>
+          <t>Dopad/výsledky</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>ex-ante</t>
+          <t>on-going</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Strategická, Operativní/procesní</t>
+          <t>Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODU5NzUxMjA3O1ByaWxvaGFETVM7RmFsc2U=</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODQ4MTk3ODQ2O1ByaWxvaGFETVM7RmFsc2U=</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>01 SEA_IROP_2021_2027_Vyhodnoceni.pdf</t>
+          <t>Housing First Charakteristika zabydlených domácností.pdf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OP Z</t>
+          <t>OP PIK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>03.044.01</t>
+          <t>01.026.04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OP Z  •  Evaluace výsledků výzvy Podpora programu Housing First (Bydlení především)</t>
+          <t>OP PIK  •  Ex post evaluace OP PIK a replikace kontrafaktuální dopadové analýzy OP PI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Evaluace výsledků výzvy Podpora programu Housing First (Bydlení především)</t>
+          <t>Ex post evaluace OP PIK a replikace kontrafaktuální dopadové analýzy OP PI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vyhodnocení dotazníku pro evaluaci dopadů programu HF pro řešení bytové nouze</t>
+          <t>Závěrečná zpráva OP PIK</t>
         </is>
       </c>
       <c r="F14" s="2">
-        <v>45289</v>
+        <v>45267</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1607,17 +1607,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Vyhodnotit přínosy projektů z výzvy na podporu pilotního rozšíření konceptu Housing First / Bydlení především pro cílové skupiny.</t>
+          <t>Komplexní souhrnná evaluace dopadů Operačního programu Podnikání a inovace pro konkurenceschopnost 2014?2020 (dále též ?OP PIK?) a opětovné kontrafaktuální vyhodnocení dopadů již dříve zpracované evaluace dopadů Operačního programu Podnikání a inovace za období 2007?2013 (déle též ?OP PI?). Primárním účelem je zjištění dopadů podpory poskytované z Evropských strukturálních a investičních fondů na konkurenceschopnost podpořených podniků, a to jak v krátkém (OP PIK), tak ve střednědobém období (OP PI). Na základě vyhodnocení se taktéž očekávají doporučení pro optimalizaci nastavení jednotlivých intervencí ve vztahu k implementaci Operačního programu Technologie a aplikace pro konkurenceschopnost 2021?2027 (dále též ?OP TAK?).</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Od června 2019 probíhá příprava podkladů (scénářů dotazníků) pro interní sběr dat u příjemců podpory a cílové skupiny. Scénář dotazníku pro cílové skupiny před nastěhováním do sociálního bydlení byl v září 2019 opilotován a od října 2019 začíná plošný sběr dat. Během 2020 dokončeny verze dotazníku po 12 měsících / 24 měsících od zabydlení domácností.</t>
+          <t>Finální vyhodnocení a shrnutí všech částí evaluace zaměřené na hodnocení dopadů OP PIK. Odpověď na evaluační otázky: 
+EO1: Jaké jsou dopady podpory na ekonomickou situaci podpořených podniků a na jejich konkurenceschopnost ve srovnání s podniky nepodpořenými?
+EO2: Jak přispěly intervence realizované v rámci OP PIK k dosahování výsledkových indikátorů?
+EO3: Bylo dosaženo výsledků, kterých měly jednotlivé specifické cíle dosáhnout?
+EO4: Jak přispěl OP PIK k plnění horizontálních zásad?</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>85 % domácností bydlelo v bytě poskytnutém v projektu alespoň 1 rok. U 89 % zabydlených se zvýšila spokojenost s bydlením. U 74 % domácností s dětmi došlo ke zkvalitnění prostoru pro děti. U 65 % zabydlených se zlepšil psychický stav (měřeno dle Kesslerovy škály psychosociální tísně). U 57 % se zvýšila spokojenost se životem (rok po zabydlení uvedlo 87 % dotázaných, že jsou spokojeni se životem).</t>
+          <t>Podpora z OP PIK, dle kontrafaktuální analýzy, částečně přispívá k posilování konkurenceschopnosti MSP. Částečně statisticky významný dopad byl nalezen v případě indikátoru přidané hodnoty, podpořené podniky také vykazovaly vyšší tvorbu tržeb, dosahovaly vyšší rentability celkového kapitálu a zvýšila se jejich celková aktiva. V případě dalších klíčových indikátorů konkurenceschopnosti ale nebyly pozorovány významné přínosy podpory. 
+Podpora jednoznačně vede ke zvyšování zaměstnanosti v podpořených podnicích. 
+Podpora ve formě finančních nástrojů (FN) přispívá k posilování konkurenceschopnosti lépe než dotační podpora.
+Klíčovým rozdílem je především to, že efekt podpory formou FN se projevuje téměř okamžitě a dlouhodobě. FN tedy lépe odpovídají na potřeby příjemců, podniky předkládají projekty, které skutečně potřebují. Výrazně pozitivnější zpětná vazba ve vztahu k FN se také projevila ve zpracovaných případových studiích. 
+OP PIK dosahuje mírně lepších výsledků v posilování konkurenceschopnosti MSP a zlepšování jejich ekonomické situace než předchozí OP PI. Mezi důvody patří především vyšší zkušenost členů implementační struktury a tlak na tematickou koncentraci, které vedou k lepší zacílenosti vyhlašovaných výzev, procesu výběru projektů i podpořených projektů samotných.
+Efekt podpory je ale velmi omezený v případě programů, zaměřených na posilování inovační kapacity podniků, jejichž efekty na zvyšování konkurenceschopnosti ani inovační výkonnosti nebyly prokázány. Podpořené projekty se ve velké většině zaměřují na inovace nižšího řádu. Roli v tomto rozhodování hraje obava o vlastní know-how, a také obava z negativních dopadů případného neúspěchu inovace, pokud by byla podpořena dotačním projektem. 
+Program téměř nijak nepřispívá k podpoře zakládání nových podniků a rozvoji podnikavosti. Dopad OP PIK je rovněž velmi nízký co se týče rozšiřování přístupu k vysokorychlostnímu internetu.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1642,22 +1652,22 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>on-going</t>
+          <t>ex-post</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Dopadová/Výsledková</t>
+          <t>Strategická, Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODQ4MTk3ODQ2O1ByaWxvaGFETVM7RmFsc2U=</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkwODUzNTI5ODtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Housing First Charakteristika zabydlených domácností.pdf</t>
+          <t>03 ZZ_Expost OP PIK.pdf</t>
         </is>
       </c>
     </row>
@@ -1669,40 +1679,514 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>06.014.01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>IROP  •  Evaluace PO1 a PO3 IROP: Případové studie</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Evaluace PO1 a PO3 IROP: Případové studie</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Evaluace PO1 a PO3 IROP</t>
+        </is>
+      </c>
+      <c r="F15" s="2">
+        <v>45267</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Vyhodnocení výsledků projektů realizovaných v rámci specifických cílů 1.1, 1.2 a 1.3 Prioritní osy 1 IROP a projektů realizovaných v rámci specifického cíle 3.1 Prioritní osy 3 IROP.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Realizace výzkumu a zpracování evaluačních zpráv.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Díky podpořeným projektům se v průměru 3,6 % obcím v každém kraji zkrátila doba jízdy do svého krajského města. Dále se na modernizovaných úsecích podařilo uspořit asi 11 % denní spotřeby energií a paliv oproti stavu před realizací projektů, a to i se zahrnutím intenzity vozidel na hodnocených silnicích, která se v ČR dlouhodobě zvyšuje. Výrazněji pozitivní byla změna u těch projektů, kde došlo k výstavbě zcela nových úseků silnic (úspora až 32 %).
+V hodnocených lokalitách a regionech lze sice zachytit požadované trendy jako např. snižování dopadů na životní prostředí, růst podílu osob využívajících MHD, snížení účasti chodců na nehodách či zlepšování klíčových socioekonomických ukazatelů, ve většině případů se ale nepodařilo prokázat, že by se daný trend odvíjel od velikosti podpory ze SC 1.2.  Menší využívání automobilové dopravy oproti situaci před projektem deklarovali např. lidé využívající terminály v Plzni nebo v Benešově nebo lidé jezdící novými trolejbusy v Hradci Králové. Tedy všude tam, kde v návaznosti na projekt došlo k dalším systémovým změnám v organizaci dopravy.
+Na základě zjištění z případových studií lze konstatovat, že hodnocené projekty v SC 1.3 přispěly pro zmírnění následků a projevů mimořádných událostí zejména tím, že zrychlily reakční časy výjezdů, a buď zvýšením dostupnosti stanic místům s výskytem mimořádných jevů nebo zefektivněním jednotlivých kroků spojených s výjezdem. 
+Z hodnocení projektů v SC 3.1 vyplynulo, že přibližně dvě třetiny projektů přispěly ke zvýšení počtu pracovních míst v regionu (vytvořením nových pracovních pozic) nebo měly pozitivní vliv na lokální ekonomiku v návaznosti na zvýšenou návštěvnost míst. Významnější vliv lze spatřovat u zcela nově zpřístupněných lokalit a památek.
+</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Dopad/výsledky</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>plnění cílů</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>ex-post</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Dopadová/Výsledková</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkxMjAzNTg1NDtQcmlsb2hhRE1TO0ZhbHNl</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>231130_Zaverecna_zprava_EvaluacePO1_3_IROP_FINAL.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PRV</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>09.003.15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PRV  •  Zpracování odpovědí na hodnotící otázky vztažené k prioritním oblastem PRV a technické pomoci PRV</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Zpracování odpovědí na hodnotící otázky vztažené k prioritním oblastem PRV a technické pomoci PRV</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Čtrnáctá zpráva o hodnocení PRV 2014-2020 - září 2023</t>
+        </is>
+      </c>
+      <c r="F16" s="2">
+        <v>45265</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Zpracování odpovědí na hodnotící otázky pro každou prioritní oblast  zahrnutou v PRV (vč. technické pomoci, Celostátní sítě pro venkov a oblasti, synergií a komplementarit ), vyhodnocení příspěvku PRV k plnění cílů SZP a Strategie EU 2020. Výstupy budou využity jako příprava pro další fáze průběžného hodnocení a ex post hodnocení, zároveň budou sloužit jako podklad pro MMR - NOK k vyhodnocení plnění cílů Dohody o partnerství.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Hodnocení PRV na datech k 30.6.2023</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">viz hodnotící zpráva  </t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Dopad/výsledky</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>on-going</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Strategická, Tematická, Dopadová/Výsledková</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTk1NjQ2MDA3NTtQcmlsb2hhRE1TO0ZhbHNl</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>230930_PHZ_2_2023_final.pdf</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>https://portal.mze.cz/public/portal/mze/dotace/program-rozvoje-venkova-na-obdobi-2014/hodnoceni-a-monitoring/hodnoceni/prubezna-zprava-o-hodnoceni-prv-zari-2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>OP Z</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>03.002.02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>OP Z  •  Evaluace národních a regionálních projektů APZ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Evaluace národních a regionálních projektů APZ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Informační a poradenská střediska</t>
+        </is>
+      </c>
+      <c r="F17" s="2">
+        <v>45260</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Jedná se o kvantitativní vyhodnocení projektů APZ na základě dat z IS ESF. 
+Bude se realizovat opakovaně, zaměří se na všechny projekty APZ.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Evaluace systémového projektu ÚP ČR s cílem vyhodnotit fungování IPS. V rámci této evaluace byly hodnoceny výsledky, kterých bylo dosaženo, a procesní stránka projektu.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Největší přínos systémového projektu PIPS představuje zdvojnásobení personálních kapacit sítě IPS ÚP ČR po dobu téměř sedmi let a vytvoření vlastního interního systému odborného vzdělávání. 
+Na druhou stranu významně zaostávalo vyhlašování veřejných zakázek, které tvořily druhý pilíř. 
+Rozporný je přínos vzniku 11 pracovišť IPS, protože na nich působil pouze projektový pracovník a s výjimkou Havířova nemají po ukončení projektu zajištěnu samostatnou existenci. 
+Slabým místem projektu je udržitelnost zejména personálního obsazení, která po jeho skončení není zajištěna. </t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Jiná</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>ad-hoc</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTk2NTA0NzU0MjtQcmlsb2hhRE1TO0ZhbHNl</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>PIPS_Zprava_Dotaznikove-setreni_Skoly.pdf</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>https://www.esfcr.cz/dalsi-dokumenty-evaluace/-/document_library_display/lFJ7WbnUo8JX/view/17016600?_110_INSTANCE_lFJ7WbnUo8JX_redirect=https%3A%2F%2Fwww.esfcr.cz%2Fdalsi-dokumenty-evaluace%2F-%2Fdocument_library_display%2FlFJ7WbnUo8JX%2Fview%2F753381%3F_110_INSTANCE_lFJ7WbnUo8JX_redirect%3Dhttps%253A%252F%252Fwww.esfcr.cz%252Fdalsi-dokumenty-evaluace%253Fp_p_id%253D110_INSTANCE_lFJ7WbnUo8JX%2526p_p_lifecycle%253D0%2526p_p_state%253Dnormal%2526p_p_mode%253Dview%2526p_p_col_id%253Dcolumn-2%2526p_p_col_pos%253D1%2526p_p_col_count%253D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>OP Z</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>03.015.01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>OP Z  •  Vyhodnocení výsledků podpory sociálních inovací v PO 3 OPZ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Vyhodnocení výsledků podpory sociálních inovací v PO 3 OPZ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Vyhodnocení výsledků podpory sociálních inovací v PO 3 OPZ</t>
+        </is>
+      </c>
+      <c r="F18" s="2">
+        <v>45260</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vyhodnocení příspěvku inovačních výzev k plnění SC PO 3  "Zvýšit kvalitu a kvantitu využívání sociálních inovací a mezinárodní spolupráce v tematických oblastech OPZ", včetně analýzy předpokladů a rizik dosažení cílů podpory. V rámci evaluace budou vyhodnoceny výzvy na podporu sociálních inovací a inovačního prostředí č. 018, 024 a 124.    </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Vyhodnocení příspěvku inovačních výzev k plnění SC PO 3  "Zvýšit kvalitu a kvantitu využívání sociálních inovací a mezinárodní spolupráce v tematických oblastech OPZ". Analýza relevantních datových zdrojů k výzvám PO 3, individuální hloubkové rozhovory a fokusní skupiny s realizátory, evaluátory a stakeholdery vybraných projektů podpořených ve výzvách PO 3, CBA vybraných projektů.
+Od první poloviny roku 2018 probíhalo ve spolupráci s oddělením 833 nastavování designu evaluace. Následně byla připravena veřejná zakázka na první vlnu kvalitativního sběru dat u realizátorů vybraných projektů podpořených v inovačních výzvách č. 24 a 124 OPZ. Tato zakázka byla realizována od května 2019 do června 2020 a navázala na ni druhá zakázka na další vlnu projektů z těchto výzev realizovaná od června 2020 do května 2021. Na základě dosavadních průběžných zjištění byla v polovině roku 2020 ve spolupráci s implementačním oddělením zahájena práce na aktualizaci evaluačního designu a předběžně naplánována převážně interně zpracovávaná část vyhodnocení (detailní monitoring podpořených projektů, případové studie vzorku projektů). Dále v druhé polovině roku 2020 začaly práce na mapování možností externího zadání CBA vybraného projektu, v prosinci proběhla předběžná tržní konzultace a v průběhu roku 2021 byla vyhlášena VZMR na realizaci a vyhodnocení uskutečnitelnosti realizace CBA v případě dvou projektů podpořených ve výzvě č. 24 OPZ. Tato zakázka byla ukončena na konci srpna 2022.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Zpráva představuje souhrnný podklad z VYHODNOCENÍ VÝSLEDKŮ PODPORY SOCIÁLNÍCH INOVACÍ V PO 3 OPZ, které bylo zahájeno v červnu roku 2018 a zahrnovalo několik etap vyhodnocení. Vzhledem ke specifické povaze Prioritní osy číslo 3 Operačního programu Zaměstnanost ? Sociální inovace a mezinárodní spolupráce, tvořily vyhodnocení samostatné a v rámci závěrů a zjištění lze pouze odkázat do jednotlivých kapitol zprávy, resp. etap evaluace představovaných samostatnými výstupy, které byly vždy v době ukončení dané etapy šířeny samostatně a sdíleny se všemi relevantními aktéry. Průběžná zjištění se tak promítala do dalšího nastavení výzev OPZ i do struktury podpory v rámci Priority 3 Operačního programu Zaměstnanost plus ? Sociální inovace.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Dopad/výsledky</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>plnění cílů</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>ex-post</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Dopadová/Výsledková</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODQzODk5MDk7UHJpbG9oYURNUztGYWxzZQ==</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>VYHODNOCENÍ VÝSLEDKŮ PODPORY SOCIÁLNÍCH INOVACÍ V PO 3 OPZ_final.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>OP PS ČR-PL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11.008.01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>OP PS ČR-PL  •  Ex-post evaluace programu Interreg V-A Česká republika - Polsko</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ex-post evaluace programu Interreg V-A Česká republika - Polsko</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>jediná etapa</t>
+        </is>
+      </c>
+      <c r="F19" s="2">
+        <v>45260</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>v realizaci</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Ex-post evaluace dlouhodobých dopadů programu.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Ex-post evaluace dlouhodobých dopadů programu</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Dopad/výsledky</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>plnění cílů</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>ex-post</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Dopadová/Výsledková</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTk0MjE0OTIyNDtQcmlsb2hhRE1TO0ZhbHNl</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>01_CZPL_ukol1_zaverecna_zprava_final.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IROP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>06.015.02</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>IROP  •  Vyhodnocení komunikačních aktivit 2018 - 2023 IROP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Vyhodnocení komunikačních aktivit 2018 - 2023 IROP</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Vyhodnocení komunikačních aktivit 2018 - 2023 IROP</t>
         </is>
       </c>
-      <c r="F15" s="2">
-        <v>45275</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>v realizaci</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="F20" s="2">
+        <v>45252</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">Evaluace komunikačních aktivit realizovaných v letech 2018-2023 
 Integrovaného regionálního operačního programu 2014-2020 a Integrovaného regionálního operačního 
 programu 2021-2027. </t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Hodnocení komunikačních aktivit navazuje na Vyhodnocení efektivity realizovaných komunikačních nástrojů ŘO IROP 2014-2020 (Deloitte, 2018),design je kombinací klasického evaluačního hodnocení (cíle, aktivity, výsledky, doporučení z předcházejícího hodnocení, 5U apod.)a marketingového hodnocení a metod, zejména vůči kampani React EU nebo webu IROP. Hlavními cíli hodnocení komunikačních nástrojů jsou: 
 - vyhodnocení komunikačních aktivit v letech 2018-2023 s akcentem na zohlednění závěrů a doporučení z Vyhodnocení efektivity realizovaných komunikačních nástrojů ŘO IROP I a posouzení dodržování principů 5U;
@@ -1715,656 +2199,87 @@
 procesní, finanční, personální apod.).</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Komunikační a publicitní aktivity vedly k naplnění cílů, byť existují konkrétní limity, kterým se v?maximální míře věnuje 14 okruhů doporučení a navazujících 37 úkolů. Pozitivně hodnoceny byly zejména komunikační aktivity zaměřené na potenciální žadatele a příjemce, hlavními a přínosnými zdroji informací pro žadatele jsou web IROP, web Centra pro regionální rozvoj (zejména konzultační servis a kontakty na zástupce Centra), osobní a telefonické konzultace a semináře. Komunikace s širokou veřejností byla komplikovanější, zároveň byl však reflektován rostoucí význam sociálních sítí. V?této souvislosti byly v posledních letech komunikační aktivity IROP upravovány podle aktuálních trendů, s důrazem na online prostředí a sociální sítě a proběhla řada úspěšných aktivit. Na základě hodnocení je navrhováno pokračovat v?komunikačních a publicitních aktivitách i v?navazujícím období. V?oblasti hodnocení a evaluací komunikačních a publicitních aktivit budou tyto aktivity postupně přecházet do širšího využívání marketingového způsobu hodnocení, kterým je možné pružněji reagovat například na probíhající kampaně a další specifické aktivity. </t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Jiná</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>plnění cílů</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>on-going</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkxMjUxNzAxNjtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>Vyhodnocení komunikačních aktivit IROP_Zaverecna_Zprava.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>OP PIK</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>01.026.04</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>OP PIK  •  Ex post evaluace OP PIK a replikace kontrafaktuální dopadové analýzy OP PI</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Ex post evaluace OP PIK a replikace kontrafaktuální dopadové analýzy OP PI</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Závěrečná zpráva OP PIK</t>
-        </is>
-      </c>
-      <c r="F16" s="2">
-        <v>45267</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Komplexní souhrnná evaluace dopadů Operačního programu Podnikání a inovace pro konkurenceschopnost 2014?2020 (dále též ?OP PIK?) a opětovné kontrafaktuální vyhodnocení dopadů již dříve zpracované evaluace dopadů Operačního programu Podnikání a inovace za období 2007?2013 (déle též ?OP PI?). Primárním účelem je zjištění dopadů podpory poskytované z Evropských strukturálních a investičních fondů na konkurenceschopnost podpořených podniků, a to jak v krátkém (OP PIK), tak ve střednědobém období (OP PI). Na základě vyhodnocení se taktéž očekávají doporučení pro optimalizaci nastavení jednotlivých intervencí ve vztahu k implementaci Operačního programu Technologie a aplikace pro konkurenceschopnost 2021?2027 (dále též ?OP TAK?).</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Finální vyhodnocení a shrnutí všech částí evaluace zaměřené na hodnocení dopadů OP PIK. Odpověď na evaluační otázky: 
-EO1: Jaké jsou dopady podpory na ekonomickou situaci podpořených podniků a na jejich konkurenceschopnost ve srovnání s podniky nepodpořenými?
-EO2: Jak přispěly intervence realizované v rámci OP PIK k dosahování výsledkových indikátorů?
-EO3: Bylo dosaženo výsledků, kterých měly jednotlivé specifické cíle dosáhnout?
-EO4: Jak přispěl OP PIK k plnění horizontálních zásad?</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Podpora z OP PIK, dle kontrafaktuální analýzy, částečně přispívá k posilování konkurenceschopnosti MSP. Částečně statisticky významný dopad byl nalezen v případě indikátoru přidané hodnoty, podpořené podniky také vykazovaly vyšší tvorbu tržeb, dosahovaly vyšší rentability celkového kapitálu a zvýšila se jejich celková aktiva. V případě dalších klíčových indikátorů konkurenceschopnosti ale nebyly pozorovány významné přínosy podpory. 
-Podpora jednoznačně vede ke zvyšování zaměstnanosti v podpořených podnicích. 
-Podpora ve formě finančních nástrojů (FN) přispívá k posilování konkurenceschopnosti lépe než dotační podpora.
-Klíčovým rozdílem je především to, že efekt podpory formou FN se projevuje téměř okamžitě a dlouhodobě. FN tedy lépe odpovídají na potřeby příjemců, podniky předkládají projekty, které skutečně potřebují. Výrazně pozitivnější zpětná vazba ve vztahu k FN se také projevila ve zpracovaných případových studiích. 
-OP PIK dosahuje mírně lepších výsledků v posilování konkurenceschopnosti MSP a zlepšování jejich ekonomické situace než předchozí OP PI. Mezi důvody patří především vyšší zkušenost členů implementační struktury a tlak na tematickou koncentraci, které vedou k lepší zacílenosti vyhlašovaných výzev, procesu výběru projektů i podpořených projektů samotných.
-Efekt podpory je ale velmi omezený v případě programů, zaměřených na posilování inovační kapacity podniků, jejichž efekty na zvyšování konkurenceschopnosti ani inovační výkonnosti nebyly prokázány. Podpořené projekty se ve velké většině zaměřují na inovace nižšího řádu. Roli v tomto rozhodování hraje obava o vlastní know-how, a také obava z negativních dopadů případného neúspěchu inovace, pokud by byla podpořena dotačním projektem. 
-Program téměř nijak nepřispívá k podpoře zakládání nových podniků a rozvoji podnikavosti. Dopad OP PIK je rovněž velmi nízký co se týče rozšiřování přístupu k vysokorychlostnímu internetu.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Dopad/výsledky</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>ex-post</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Strategická, Dopadová/Výsledková</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkwODUzNTI5ODtQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>03 ZZ_Expost OP PIK.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>IROP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>06.014.01</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>IROP  •  Evaluace PO1 a PO3 IROP: Případové studie</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Evaluace PO1 a PO3 IROP: Případové studie</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Evaluace PO1 a PO3 IROP</t>
-        </is>
-      </c>
-      <c r="F17" s="2">
-        <v>45267</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Vyhodnocení výsledků projektů realizovaných v rámci specifických cílů 1.1, 1.2 a 1.3 Prioritní osy 1 IROP a projektů realizovaných v rámci specifického cíle 3.1 Prioritní osy 3 IROP.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Realizace výzkumu a zpracování evaluačních zpráv.</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Díky podpořeným projektům se v průměru 3,6 % obcím v každém kraji zkrátila doba jízdy do svého krajského města. Dále se na modernizovaných úsecích podařilo uspořit asi 11 % denní spotřeby energií a paliv oproti stavu před realizací projektů, a to i se zahrnutím intenzity vozidel na hodnocených silnicích, která se v ČR dlouhodobě zvyšuje. Výrazněji pozitivní byla změna u těch projektů, kde došlo k výstavbě zcela nových úseků silnic (úspora až 32 %).
-V hodnocených lokalitách a regionech lze sice zachytit požadované trendy jako např. snižování dopadů na životní prostředí, růst podílu osob využívajících MHD, snížení účasti chodců na nehodách či zlepšování klíčových socioekonomických ukazatelů, ve většině případů se ale nepodařilo prokázat, že by se daný trend odvíjel od velikosti podpory ze SC 1.2.  Menší využívání automobilové dopravy oproti situaci před projektem deklarovali např. lidé využívající terminály v Plzni nebo v Benešově nebo lidé jezdící novými trolejbusy v Hradci Králové. Tedy všude tam, kde v návaznosti na projekt došlo k dalším systémovým změnám v organizaci dopravy.
-Na základě zjištění z případových studií lze konstatovat, že hodnocené projekty v SC 1.3 přispěly pro zmírnění následků a projevů mimořádných událostí zejména tím, že zrychlily reakční časy výjezdů, a buď zvýšením dostupnosti stanic místům s výskytem mimořádných jevů nebo zefektivněním jednotlivých kroků spojených s výjezdem. 
-Z hodnocení projektů v SC 3.1 vyplynulo, že přibližně dvě třetiny projektů přispěly ke zvýšení počtu pracovních míst v regionu (vytvořením nových pracovních pozic) nebo měly pozitivní vliv na lokální ekonomiku v návaznosti na zvýšenou návštěvnost míst. Významnější vliv lze spatřovat u zcela nově zpřístupněných lokalit a památek.
-</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Dopad/výsledky</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>plnění cílů</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>ex-post</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Dopadová/Výsledková</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkxMjAzNTg1NDtQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>231130_Zaverecna_zprava_EvaluacePO1_3_IROP_FINAL.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>PRV</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>09.003.15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PRV  •  Zpracování odpovědí na hodnotící otázky vztažené k prioritním oblastem PRV a technické pomoci PRV</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Zpracování odpovědí na hodnotící otázky vztažené k prioritním oblastem PRV a technické pomoci PRV</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Čtrnáctá zpráva o hodnocení PRV 2014-2020 - září 2023</t>
-        </is>
-      </c>
-      <c r="F18" s="2">
-        <v>45265</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Zpracování odpovědí na hodnotící otázky pro každou prioritní oblast  zahrnutou v PRV (vč. technické pomoci, Celostátní sítě pro venkov a oblasti, synergií a komplementarit ), vyhodnocení příspěvku PRV k plnění cílů SZP a Strategie EU 2020. Výstupy budou využity jako příprava pro další fáze průběžného hodnocení a ex post hodnocení, zároveň budou sloužit jako podklad pro MMR - NOK k vyhodnocení plnění cílů Dohody o partnerství.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Hodnocení PRV na datech k 30.6.2023</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">viz hodnotící zpráva  </t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Dopad/výsledky</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>on-going</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Strategická, Tematická, Dopadová/Výsledková</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTk1NjQ2MDA3NTtQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>230930_PHZ_2_2023_final.pdf</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>https://portal.mze.cz/public/portal/mze/dotace/program-rozvoje-venkova-na-obdobi-2014/hodnoceni-a-monitoring/hodnoceni/prubezna-zprava-o-hodnoceni-prv-zari-2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>OP Z</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>03.002.02</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>OP Z  •  Evaluace národních a regionálních projektů APZ</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Evaluace národních a regionálních projektů APZ</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Informační a poradenská střediska</t>
-        </is>
-      </c>
-      <c r="F19" s="2">
-        <v>45260</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Jedná se o kvantitativní vyhodnocení projektů APZ na základě dat z IS ESF. 
-Bude se realizovat opakovaně, zaměří se na všechny projekty APZ.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Evaluace systémového projektu ÚP ČR s cílem vyhodnotit fungování IPS. V rámci této evaluace byly hodnoceny výsledky, kterých bylo dosaženo, a procesní stránka projektu.</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Největší přínos systémového projektu PIPS představuje zdvojnásobení personálních kapacit sítě IPS ÚP ČR po dobu téměř sedmi let a vytvoření vlastního interního systému odborného vzdělávání. 
-Na druhou stranu významně zaostávalo vyhlašování veřejných zakázek, které tvořily druhý pilíř. 
-Rozporný je přínos vzniku 11 pracovišť IPS, protože na nich působil pouze projektový pracovník a s výjimkou Havířova nemají po ukončení projektu zajištěnu samostatnou existenci. 
-Slabým místem projektu je udržitelnost zejména personálního obsazení, která po jeho skončení není zajištěna. </t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Jiná</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>ad-hoc</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTk2NTA0NzU0MjtQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>PIPS_Zprava_Dotaznikove-setreni_Skoly.pdf</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>https://www.esfcr.cz/dalsi-dokumenty-evaluace/-/document_library_display/lFJ7WbnUo8JX/view/17016600?_110_INSTANCE_lFJ7WbnUo8JX_redirect=https%3A%2F%2Fwww.esfcr.cz%2Fdalsi-dokumenty-evaluace%2F-%2Fdocument_library_display%2FlFJ7WbnUo8JX%2Fview%2F753381%3F_110_INSTANCE_lFJ7WbnUo8JX_redirect%3Dhttps%253A%252F%252Fwww.esfcr.cz%252Fdalsi-dokumenty-evaluace%253Fp_p_id%253D110_INSTANCE_lFJ7WbnUo8JX%2526p_p_lifecycle%253D0%2526p_p_state%253Dnormal%2526p_p_mode%253Dview%2526p_p_col_id%253Dcolumn-2%2526p_p_col_pos%253D1%2526p_p_col_count%253D2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>OP Z</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>03.015.01</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>OP Z  •  Vyhodnocení výsledků podpory sociálních inovací v PO 3 OPZ</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Vyhodnocení výsledků podpory sociálních inovací v PO 3 OPZ</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Vyhodnocení výsledků podpory sociálních inovací v PO 3 OPZ</t>
-        </is>
-      </c>
-      <c r="F20" s="2">
-        <v>45260</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vyhodnocení příspěvku inovačních výzev k plnění SC PO 3  "Zvýšit kvalitu a kvantitu využívání sociálních inovací a mezinárodní spolupráce v tematických oblastech OPZ", včetně analýzy předpokladů a rizik dosažení cílů podpory. V rámci evaluace budou vyhodnoceny výzvy na podporu sociálních inovací a inovačního prostředí č. 018, 024 a 124.    </t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Vyhodnocení příspěvku inovačních výzev k plnění SC PO 3  "Zvýšit kvalitu a kvantitu využívání sociálních inovací a mezinárodní spolupráce v tematických oblastech OPZ". Analýza relevantních datových zdrojů k výzvám PO 3, individuální hloubkové rozhovory a fokusní skupiny s realizátory, evaluátory a stakeholdery vybraných projektů podpořených ve výzvách PO 3, CBA vybraných projektů.
-Od první poloviny roku 2018 probíhalo ve spolupráci s oddělením 833 nastavování designu evaluace. Následně byla připravena veřejná zakázka na první vlnu kvalitativního sběru dat u realizátorů vybraných projektů podpořených v inovačních výzvách č. 24 a 124 OPZ. Tato zakázka byla realizována od května 2019 do června 2020 a navázala na ni druhá zakázka na další vlnu projektů z těchto výzev realizovaná od června 2020 do května 2021. Na základě dosavadních průběžných zjištění byla v polovině roku 2020 ve spolupráci s implementačním oddělením zahájena práce na aktualizaci evaluačního designu a předběžně naplánována převážně interně zpracovávaná část vyhodnocení (detailní monitoring podpořených projektů, případové studie vzorku projektů). Dále v druhé polovině roku 2020 začaly práce na mapování možností externího zadání CBA vybraného projektu, v prosinci proběhla předběžná tržní konzultace a v průběhu roku 2021 byla vyhlášena VZMR na realizaci a vyhodnocení uskutečnitelnosti realizace CBA v případě dvou projektů podpořených ve výzvě č. 24 OPZ. Tato zakázka byla ukončena na konci srpna 2022.</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Zpráva představuje souhrnný podklad z VYHODNOCENÍ VÝSLEDKŮ PODPORY SOCIÁLNÍCH INOVACÍ V PO 3 OPZ, které bylo zahájeno v červnu roku 2018 a zahrnovalo několik etap vyhodnocení. Vzhledem ke specifické povaze Prioritní osy číslo 3 Operačního programu Zaměstnanost ? Sociální inovace a mezinárodní spolupráce, tvořily vyhodnocení samostatné a v rámci závěrů a zjištění lze pouze odkázat do jednotlivých kapitol zprávy, resp. etap evaluace představovaných samostatnými výstupy, které byly vždy v době ukončení dané etapy šířeny samostatně a sdíleny se všemi relevantními aktéry. Průběžná zjištění se tak promítala do dalšího nastavení výzev OPZ i do struktury podpory v rámci Priority 3 Operačního programu Zaměstnanost plus ? Sociální inovace.</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Dopad/výsledky</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>plnění cílů</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>ex-post</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Dopadová/Výsledková</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODQzODk5MDk7UHJpbG9oYURNUztGYWxzZQ==</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>VYHODNOCENÍ VÝSLEDKŮ PODPORY SOCIÁLNÍCH INOVACÍ V PO 3 OPZ_final.pdf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OP PS ČR-PL</t>
+          <t>NOK (MMR)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11.008.01</t>
+          <t>NOK.002.11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OP PS ČR-PL  •  Ex-post evaluace programu Interreg V-A Česká republika - Polsko</t>
+          <t>NOK (MMR)  •  Vyhodnocení komunikačních aktivit NOK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ex-post evaluace programu Interreg V-A Česká republika - Polsko</t>
+          <t>Vyhodnocení komunikačních aktivit NOK</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>jediná etapa</t>
+          <t>Hodnocení povědomí veřejnosti o problematice fondů EU 2023 - Podzim 2023</t>
         </is>
       </c>
       <c r="F21" s="2">
-        <v>45260</v>
+        <v>45245</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>v realizaci</t>
+          <t>ukončeno</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
-        <is>
-          <t>Ex-post evaluace dlouhodobých dopadů programu.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ex-post evaluace dlouhodobých dopadů programu</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Dopad/výsledky</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>plnění cílů</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>ex-post</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Dopadová/Výsledková</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTk0MjE0OTIyNDtQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>01_CZPL_ukol1_zaverecna_zprava_final.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NOK (MMR)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NOK.002.11</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>NOK (MMR)  •  Vyhodnocení komunikačních aktivit NOK</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Vyhodnocení komunikačních aktivit NOK</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Hodnocení povědomí veřejnosti o problematice fondů EU 2023 - Podzim 2023</t>
-        </is>
-      </c>
-      <c r="F22" s="2">
-        <v>45245</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
         <is>
           <t>Kvalitativní vyhodnocení komunikačních aktivit Národního orgánu pro koordinaci zrealizovaných za dané období. Výsledky budou použity pro nastavení další komunikační strategie v navazujících ročních komunikačních plánech.
 Předmětem hodnocení:
@@ -2373,12 +2288,12 @@
 ? průběžná kontrola naplňování cílových hodnot indikátorů stanovených ve Společné komunikační strategii 2014?2020 v oblasti komunikace fondů EU (Míra informovanosti o fondech EU u cílové skupiny; Míra znalosti podpořených projektů u cílové skupiny; Míra povědomí široké veřejnosti o fondech EU).</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Cílem hodnocení bylo zjistit aktuální povědomí široké veřejnosti o problematice fondů EU po informační kampani zaměřené na problematiku projektů podpořených v oblasti životního prostředí. Šetření ukázalo, že fondy EU zná 86 % dotázaných, povědomí o konkrétním projektu má 64 %. Pro většinu dotázaných byla realizovaná kampaň srozumitelná a důvěryhodná.</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">Členství ČR v EU vnímá pozitivně 48 % dotázaných (Příznivci), opačný názor má 8 % (Odpůrci). Neutrální vztah (Neutrální) nebo žádný názor má 44 % respondentů. Od posledního šetření (jaro 2023) vzrostl podíl Příznivců, a to především na úkor Odpůrců a Neutrálních.
 Povědomí o fondech EU má 86 % dotázaných, což je možné považovat za podstatné zlepšení oproti situaci před informační kampaní, kdy povědomí o fondech EU měly 3/4 dotázaných. 
@@ -2392,87 +2307,87 @@
 </t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Jiná</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>publicita</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>on-going</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Tematická</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkyOTQwOTc4MTtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>Povědomí o fondech EU_Podzim 2023.pdf</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>OP Z</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>03.009.01</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>OP Z  •  Hodnocení dopadů podpory sociálního podnikání</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Hodnocení dopadů podpory sociálního podnikání</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Průběžné dotazníkové šetření u sociálních podnikatelů a podpořených osob</t>
         </is>
       </c>
-      <c r="F23" s="2">
+      <c r="F22" s="2">
         <v>45230</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>ukončeno</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>PO 2 - IP 2.1 - SC2:  Rozvoj sektoru sociální ekonomiky
 + podpořené sociální podniky v PO 2 - IP 2.1 - SC1 (Výzvy na koordinovaný přístup k řešení sociálně vyloučených lokalit SVL) a PO 2 - IP 2.3 - SC1 (Strategie komunitně vedeného místního rozvoje)
@@ -2485,17 +2400,113 @@
 ? zhodnocení procesu</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Průběžné interní dotazníkové šetření u sociálních podnikatelů. Průběžně probíhá sběr dat z interního průběžného dotazníku pro příjemce podpory - sociální podnikatele a průběžný sběr dat z dotazníku pro podpořené osoby zaměřeného na přínosy v rámci zlepšení pozice na trhu práce. V lednu 2019 zpracována průběžná zpráva Vyhodnocení šetření sociálních podniků: výzvy OPZ č. 15, 26, 47 a 67 po 12 měsících. V srpnu 2021 byla zpracována průběžná zpráva Vyhodnocení šetření sociálních podniků po 6 měsících od začátku podpory z OPZ.</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Provoz sociálně-integračního podniku udrželo 12 měsíců od konce podpory 81 procent podpořených projektů. Dle přísnějšího kritéria pokračovalo v podnikání bez výraznějšího krácení pracovních úvazků 62 procent podpořených organizací (či podnikajících osob).
 Účast v projektu ? zaměstnání v sociálním podniku ? měla celkově pozitivní efekt na cílovou skupinu v rámci vývoje postavení na trhu práce. Přesto, že po konci projektu znatelně klesl podíl zaměstnaných a OSVČ (na 68 procent dva roky po konci projektu), tento stav je o 15 p. b. lepší, než byl dva roky před vstupem do projektu, kdy bylo zaměstnaných 53 procent podpořených osob. Dva roky po konci v projektu byl nižší podíl neaktivních osob (o 9 p. b.; pokles z 30 procent na 21 procent) i nezaměstnaných (o 5 p. b.; pokles ze 17 procent na 12 procent).</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Dopad/výsledky</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>plnění cílů</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>on-going</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Operativní/procesní, Dopadová/Výsledková</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MzI1NjA1NTMwO1ByaWxvaGFETVM7RmFsc2U=</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Vyhodnocení šetření SPOD_výzva 15_průběžná zpráva (2017).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OP Z</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>03.038.01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>OP Z  •  Dotazníkové šetření u příjemců soutěžních projektů OPZ (Dotazník ZoR)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Dotazníkové šetření u příjemců soutěžních projektů OPZ (Dotazník ZoR)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Dotazníkové šetření u příjemců soutěžních projektů OPZ (Dotazník ZoR)</t>
+        </is>
+      </c>
+      <c r="F23" s="2">
+        <v>45230</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soutěžní projekty OPZ: konečné výsledky a přínosy projektů, problémy v realizaci, horizontální témata (rovnost žen a mužů) apod. Pravidelné nebo ad-hoc hodnocení na základě výstupů dotazníku, který bude v OPZ povinnou součástí  závěrečných zpráv o realizaci (ZoR) soutěžních projektů.  </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>04/2017 Zahájen průbežný sběr dat formou elektronického dotazníku povinného pro příjemce v rámci závěrečných ZoR. První průběžná zpráva zpracována v dubnu 2019. Druhá průběžná zpráva byla zpracována v květnu roku 2021 a do tohoto vyhodnocení bylo zahrnuto 3869 odpovědí.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Ve skupině projektů, které ve svých aktivitách pracovaly přímo s klienty služeb, byly nejčastěji zastoupenou cílovou skupinou osoby se znevýhodněním, sociálně vyloučené nebo sociálním vyloučením ohrožené osoby (53 procent projektů), dále pak rodiče, osoby pečující o děti či závislé osoby, neformální pečovatelé (38 procent projektů) a nezaměstnaní, nezaměstnaností ohrožení či neaktivní/práci nehledající jedinci (pracovalo s ní 24 procent projektů). V 58 procentech projektů, které ve svých aktivitách pracovaly přímo s klienty služeb, získali někteří nezaměstnaní účastníci práci. 11 z 25. Ve 33 procentech projektů, které ve svých aktivitách pracovaly přímo s klienty služeb, začali účastníci využívat ve významnějším rozsahu flexibilních forem organizace práce. Osmdesát osm procent projektů, které ve svých aktivitách pracovaly přímo s klienty služeb, uvedlo, že se díky projektovým aktivitám změnily postoje a motivace některých účastníků.
+věku, nejčastěji dosaženou změnu viděli v umožněných či usnadněných návratech rodičů z mateřské či rodičovské dovolené do pracovního procesu (97 procent projektů). Druhou nejčastěji zmiňovanou dosaženou změnou byla kratší průměrná doba, kterou rodiče tráví na rodičovské dovolené ? tento přínos zaznamenalo 69 procent projektů. 58 procent projektů pak zaznamenalo zvýšení úvazků rodičů s předškolními dětmi. Méně často bylo díky projektům dosaženo zavedení či rozšíření flexibilní pracovní doby či částečných úvazků (36 procent projektů). Téměř třetina projektů pak také zaznamenala větší zájem o práci v organizaci díky zařízení péče o děti, vyšší spokojenost a loajalitu zaměstnanců, lepší atmosféru na pracovišti.</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>Ano</t>
@@ -2516,11 +2527,6 @@
           <t>Dopad/výsledky</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>plnění cílů</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>on-going</t>
@@ -2533,146 +2539,55 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MzI1NjA1NTMwO1ByaWxvaGFETVM7RmFsc2U=</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7NTYwMTEzNzU4O1ByaWxvaGFETVM7RmFsc2U=</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Vyhodnocení šetření SPOD_výzva 15_průběžná zpráva (2017).pdf</t>
+          <t>1. průběžné vyhodnocení dotazníku ZoR.pdf.pdf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OP Z</t>
+          <t>NOK (MMR)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>03.038.01</t>
+          <t>NOK.021.01</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OP Z  •  Dotazníkové šetření u příjemců soutěžních projektů OPZ (Dotazník ZoR)</t>
+          <t>NOK (MMR)  •  Výsledková evaluace přínosů evropských fondů na regionální úrovni</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Dotazníkové šetření u příjemců soutěžních projektů OPZ (Dotazník ZoR)</t>
+          <t>Výsledková evaluace přínosů evropských fondů na regionální úrovni</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dotazníkové šetření u příjemců soutěžních projektů OPZ (Dotazník ZoR)</t>
+          <t>Výsledková evaluace přínosů evropských fondů na regionální úrovni</t>
         </is>
       </c>
       <c r="F24" s="2">
-        <v>45230</v>
+        <v>45225</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ukončeno</t>
+          <t>v realizaci</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soutěžní projekty OPZ: konečné výsledky a přínosy projektů, problémy v realizaci, horizontální témata (rovnost žen a mužů) apod. Pravidelné nebo ad-hoc hodnocení na základě výstupů dotazníku, který bude v OPZ povinnou součástí  závěrečných zpráv o realizaci (ZoR) soutěžních projektů.  </t>
+          <t>Vyhodnocení vybraných cílů územního rozvoje v Česku a přínosů evropských fondů na regionální úrovni.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>04/2017 Zahájen průbežný sběr dat formou elektronického dotazníku povinného pro příjemce v rámci závěrečných ZoR. První průběžná zpráva zpracována v dubnu 2019. Druhá průběžná zpráva byla zpracována v květnu roku 2021 a do tohoto vyhodnocení bylo zahrnuto 3869 odpovědí.</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Ve skupině projektů, které ve svých aktivitách pracovaly přímo s klienty služeb, byly nejčastěji zastoupenou cílovou skupinou osoby se znevýhodněním, sociálně vyloučené nebo sociálním vyloučením ohrožené osoby (53 procent projektů), dále pak rodiče, osoby pečující o děti či závislé osoby, neformální pečovatelé (38 procent projektů) a nezaměstnaní, nezaměstnaností ohrožení či neaktivní/práci nehledající jedinci (pracovalo s ní 24 procent projektů). V 58 procentech projektů, které ve svých aktivitách pracovaly přímo s klienty služeb, získali někteří nezaměstnaní účastníci práci. 11 z 25. Ve 33 procentech projektů, které ve svých aktivitách pracovaly přímo s klienty služeb, začali účastníci využívat ve významnějším rozsahu flexibilních forem organizace práce. Osmdesát osm procent projektů, které ve svých aktivitách pracovaly přímo s klienty služeb, uvedlo, že se díky projektovým aktivitám změnily postoje a motivace některých účastníků.
-věku, nejčastěji dosaženou změnu viděli v umožněných či usnadněných návratech rodičů z mateřské či rodičovské dovolené do pracovního procesu (97 procent projektů). Druhou nejčastěji zmiňovanou dosaženou změnou byla kratší průměrná doba, kterou rodiče tráví na rodičovské dovolené ? tento přínos zaznamenalo 69 procent projektů. 58 procent projektů pak zaznamenalo zvýšení úvazků rodičů s předškolními dětmi. Méně často bylo díky projektům dosaženo zavedení či rozšíření flexibilní pracovní doby či částečných úvazků (36 procent projektů). Téměř třetina projektů pak také zaznamenala větší zájem o práci v organizaci díky zařízení péče o děti, vyšší spokojenost a loajalitu zaměstnanců, lepší atmosféru na pracovišti.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Dopad/výsledky</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>on-going</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Operativní/procesní, Dopadová/Výsledková</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7NTYwMTEzNzU4O1ByaWxvaGFETVM7RmFsc2U=</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>1. průběžné vyhodnocení dotazníku ZoR.pdf.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>NOK (MMR)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NOK.021.01</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>NOK (MMR)  •  Výsledková evaluace přínosů evropských fondů na regionální úrovni</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Výsledková evaluace přínosů evropských fondů na regionální úrovni</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Výsledková evaluace přínosů evropských fondů na regionální úrovni</t>
-        </is>
-      </c>
-      <c r="F25" s="2">
-        <v>45225</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>v realizaci</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Vyhodnocení vybraných cílů územního rozvoje v Česku a přínosů evropských fondů na regionální úrovni.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">Vyhodnocení vybraných cílů územního rozvoje v Česku a přínosů evropských fondů na regionální úrovni.
 Evaluace odpoví na otázky:
@@ -2686,6 +2601,101 @@
 </t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Dopad/výsledky</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>územní dimenze a integrované nástroje</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>on-going</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Dopadová/Výsledková</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkzNDk5OTE1ODtQcmlsb2hhRE1TO0ZhbHNl</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>MMR Regiony_Úkol 7_Záverečná zpráva.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OP VVV</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>02.006.03</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>OP VVV  •  Evaluace IPs PO 3 OP VVV - III.: Evaluace systémového projektu "SYPO"</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Evaluace IPs PO 3 OP VVV - III.: Evaluace systémového projektu "SYPO"</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Evaluace IPs PO 3 OP VVV - III.: Evaluace systémového projektu "SYPO": Závěrečná zpráva</t>
+        </is>
+      </c>
+      <c r="F25" s="2">
+        <v>45216</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Hodnocení účelnosti a účinnosti intervencí při dosahování cílů individuálních projektů systémových (IPs) a individuálních projektů s koncepčním charakterem  (IPk) PO3</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Závěrečné vyhodnocení všech evaluačních otázek</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Realizace projektu a jeho aktivit proběhla v souladu s naplánovaným harmonogramem. Došlo k naplnění všech dílčích cílů projektu. Existovala rizika a bariéry, která částečně ohrožovali realizaci projektu. V projektu byly vhodně nastavené interní evaluace. Model systému hodnocení kvality DVPP přispívá k zajištění kvalitního vzdělávání pedagogických pracovníků. V projektu byla vhodně nastavená podpora pro vedení škol a aktivity přispívají k plnění stanovených cílů KA Management. Webináře zaměřené na oborové novinky byly hodnoceny pozitivně a přispívají k rozvoji pedagogů. Projekt přispívá k podpoře začínajících učitelů a aktivity přispívají k plnění stanovených cílů KA Začínající učitel. Vybudování sítě kabinetů od národní až po oblastní je hodnoceno jako přínosné, problémová byla rozdílná a nevyjasněná očekávání. Nekoordinované konkurenční projekty vedly k přesycenosti terénu. Projekt SYPO realizoval aktivity, které přispěli k seznamování veřejnosti s projektem a jeho aktivitami. Nejčastější formou spolupráce IPs byly odborné panely. V průběhu projektu nedošlo k nezamýšleným dopadům.</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>Ano</t>
@@ -2698,7 +2708,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Ne</t>
+          <t>Ano</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2706,11 +2716,6 @@
           <t>Dopad/výsledky</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>územní dimenze a integrované nástroje</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>on-going</t>
@@ -2718,48 +2723,48 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Dopadová/Výsledková</t>
+          <t>Operativní/procesní, Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkzNDk5OTE1ODtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTIwNjgyMTQyMTtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>MMR Regiony_Úkol 7_Záverečná zpráva.pdf</t>
+          <t>SYPO_Závěrečná zpráva.pdf</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OP VVV</t>
+          <t>NOK (MMR)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>02.006.03</t>
+          <t>NOK.022.01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>OP VVV  •  Evaluace IPs PO 3 OP VVV - III.: Evaluace systémového projektu "SYPO"</t>
+          <t>NOK (MMR)  •  Výsledková tematická evaluace Dohody o partnerství pro programové období 2014-2020</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Evaluace IPs PO 3 OP VVV - III.: Evaluace systémového projektu "SYPO"</t>
+          <t>Výsledková tematická evaluace Dohody o partnerství pro programové období 2014-2020</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Evaluace IPs PO 3 OP VVV - III.: Evaluace systémového projektu "SYPO": Závěrečná zpráva</t>
+          <t>Výsledková tematická evaluace Dohody o partnerství 2014-2020: výstupy</t>
         </is>
       </c>
       <c r="F26" s="2">
-        <v>45216</v>
+        <v>45192</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2768,105 +2773,15 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hodnocení účelnosti a účinnosti intervencí při dosahování cílů individuálních projektů systémových (IPs) a individuálních projektů s koncepčním charakterem  (IPk) PO3</t>
+          <t>Cílem evaluace je na celostátní /národní úrovni kvantifikovat, interpretovat a vyhodnotit výsledky či dopady programů financovaných z Evropských strukturálních a investičních fondů (ESIF) , a to zejména z pohledu jejich příspěvku k naplňování očekávaných výsledků jednotlivých tematických cílů definovaných Dohodou o partnerství 2014-2020. Účelem evaluace je přinést ucelený pohled na programové období 2014-2020 zejména z hlediska toho, na co byly prostředky ESIF využit a jakých výsledků a přínosů (dopadů) bylo dosaženo v rámci jednotlivých tematických cílů. Evaluace také vyhodnotí využití prostředků REACT-EU v ČR. Předmětem evaluace je také vyhodnocení efektu synergických a komplementárních vazeb v rámci a mezi tematickými cíli.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Závěrečné vyhodnocení všech evaluačních otázek</t>
+          <t xml:space="preserve">Cílem evaluace je na celostátní / národní úrovni kvantifikovat, interpretovat a vyhodnotit výsledky či dopady programů financovaných z Evropských strukturálních a investičních fondů (ESIF), a to zejména z pohledu jejich příspěvku k naplňování očekávaných výsledků jednotlivých tematických cílů definovaných Dohodou o partnerství pro programové období 2014?2020. Účelem evaluace je přinést ucelený pohled na programové období 2014?2020 zejména z hlediska toho, na co byly prostředky ESI fondů využity a jakých výsledků a přínosů (dopadů) bylo dosaženo v rámci jednotlivých tematických oblastí vymezených tematickými cíli. Evaluace také vyhodnotí využití prostředků REACT-EU v ČR. Předmětem evaluace bude rovněž vyhodnocení efektu synergických a komplementárních vazeb v rámci a mezi tematickými cíli. V rámci evaluace bude rovněž zjišťováno, co se v programovém období 2014?2020 osvědčilo a co lze použít v následujícím programovém období 2021+. </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
-        <is>
-          <t>Realizace projektu a jeho aktivit proběhla v souladu s naplánovaným harmonogramem. Došlo k naplnění všech dílčích cílů projektu. Existovala rizika a bariéry, která částečně ohrožovali realizaci projektu. V projektu byly vhodně nastavené interní evaluace. Model systému hodnocení kvality DVPP přispívá k zajištění kvalitního vzdělávání pedagogických pracovníků. V projektu byla vhodně nastavená podpora pro vedení škol a aktivity přispívají k plnění stanovených cílů KA Management. Webináře zaměřené na oborové novinky byly hodnoceny pozitivně a přispívají k rozvoji pedagogů. Projekt přispívá k podpoře začínajících učitelů a aktivity přispívají k plnění stanovených cílů KA Začínající učitel. Vybudování sítě kabinetů od národní až po oblastní je hodnoceno jako přínosné, problémová byla rozdílná a nevyjasněná očekávání. Nekoordinované konkurenční projekty vedly k přesycenosti terénu. Projekt SYPO realizoval aktivity, které přispěli k seznamování veřejnosti s projektem a jeho aktivitami. Nejčastější formou spolupráce IPs byly odborné panely. V průběhu projektu nedošlo k nezamýšleným dopadům.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Dopad/výsledky</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>on-going</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Operativní/procesní, Dopadová/Výsledková</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTIwNjgyMTQyMTtQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>SYPO_Závěrečná zpráva.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>NOK (MMR)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NOK.022.01</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>NOK (MMR)  •  Výsledková tematická evaluace Dohody o partnerství pro programové období 2014-2020</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Výsledková tematická evaluace Dohody o partnerství pro programové období 2014-2020</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Výsledková tematická evaluace Dohody o partnerství 2014-2020: výstupy</t>
-        </is>
-      </c>
-      <c r="F27" s="2">
-        <v>45192</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Cílem evaluace je na celostátní /národní úrovni kvantifikovat, interpretovat a vyhodnotit výsledky či dopady programů financovaných z Evropských strukturálních a investičních fondů (ESIF) , a to zejména z pohledu jejich příspěvku k naplňování očekávaných výsledků jednotlivých tematických cílů definovaných Dohodou o partnerství 2014-2020. Účelem evaluace je přinést ucelený pohled na programové období 2014-2020 zejména z hlediska toho, na co byly prostředky ESIF využit a jakých výsledků a přínosů (dopadů) bylo dosaženo v rámci jednotlivých tematických cílů. Evaluace také vyhodnotí využití prostředků REACT-EU v ČR. Předmětem evaluace je také vyhodnocení efektu synergických a komplementárních vazeb v rámci a mezi tematickými cíli.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cílem evaluace je na celostátní / národní úrovni kvantifikovat, interpretovat a vyhodnotit výsledky či dopady programů financovaných z Evropských strukturálních a investičních fondů (ESIF), a to zejména z pohledu jejich příspěvku k naplňování očekávaných výsledků jednotlivých tematických cílů definovaných Dohodou o partnerství pro programové období 2014?2020. Účelem evaluace je přinést ucelený pohled na programové období 2014?2020 zejména z hlediska toho, na co byly prostředky ESI fondů využity a jakých výsledků a přínosů (dopadů) bylo dosaženo v rámci jednotlivých tematických oblastí vymezených tematickými cíli. Evaluace také vyhodnotí využití prostředků REACT-EU v ČR. Předmětem evaluace bude rovněž vyhodnocení efektu synergických a komplementárních vazeb v rámci a mezi tematickými cíli. V rámci evaluace bude rovněž zjišťováno, co se v programovém období 2014?2020 osvědčilo a co lze použít v následujícím programovém období 2021+. </t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
         <is>
           <t xml:space="preserve">Do budoucna by se ESIF měly koncentrovat do několika prioritních oblastí. Intenzivnějším využívaním finančních nástrojů a zajištěním navazujícího financování může ČR zvýšit dopad podpory ESIF.
 TC1: Bez ESIF by počet aplikačních výsledků byl o cca třetinu nižší. ESIF podporují rozvoj infrastruktury pro rozvoj aplikovaného výzkumu a spolupráce mezi výzkumnými organizacemi a aplikační sférou. ESIF mají prokazatelně pozitivní vliv na příjmy VŠ ze smluvního výzkumu  a z transferu technologií obecně. Bez podpory z ESIF by příjmy VŠ v přepočtu na celkové příjmy v obou těchto kategoriích pravděpodobně poklesly.
@@ -2883,6 +2798,98 @@
 </t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Dopad/výsledky</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>on-going</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Strategická, Tematická, Dopadová/Výsledková</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTc4MDU4OTE1NjtQcmlsb2hhRE1TO0ZhbHNl</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>TC3_PZ_leták_final_en (1).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>OP Z</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>03.010.03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>OP Z  •  Sběr dat pro OPZ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sběr dat pro OPZ</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Realizace a vyhodnocení fokusních skupin</t>
+        </is>
+      </c>
+      <c r="F27" s="2">
+        <v>45184</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Realizace fokusních skupin a dalších šetření za účelem sběru dat pro OPZ. Výstupy z těchto šetření nejsou samostatnými evaluacemi, ale slouží jako dílčí vstupy pro jiné, komplexní evaluace OPZ nebo jako samostatné analytické podklady.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Realizace a vyhodnocení tematicky zaměřených fokusních skupin
+Zakázka reagovala na nedostatek informací kvalitativního charakteru v řadě výzkumných a implementačních oblastí od přístupu realizátorů projektů v sociální oblasti, přes pohled zástupců samospráv na předškolní péči až po zkušenosti zaměstnavatelů s projekty Úřadu práce ČR. Získané poznatky budou využity pro optimalizaci procesu implementace OPZ+, a také jako doplňující informační zdroj pro lepší zacílení plánovaných výzev či projektů. V neposlední řadě se získané závěry stanou součástí dalších evaluačních výstupů. </t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zakázka přinesla různorodá zjištění v osmi samostatných tematických oblastech.
+Např. v oblasti spolupráce ÚP ČR je jedním ze zjištění, že nestátní neziskové organizace a většina obcí zastoupených v diskuzi považuje spolupráci s ÚP ČR a jeho dotační podporu za klíčový nástroj pro začleňování zranitelných skupin na trh práce a pro jejich sociální integraci. Jako problematický však organizace identifikují zdlouhavý proces vyřizování příspěvků na mzdové náklady podpořených osob, ztížené podmínky jejich včasného plánování, byrokratickou a administrativní zátěž. Řada dalších zjištění, a to rovněž v ostatních tématech, je uvedena v samostatné příloze. </t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Ano</t>
@@ -2900,27 +2907,27 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Dopad/výsledky</t>
+          <t>Jiná</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>on-going</t>
+          <t>ad-hoc</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Strategická, Tematická, Dopadová/Výsledková</t>
+          <t>Operativní/procesní, Tematická</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTc4MDU4OTE1NjtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTgwOTQ4MTg4NjtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>TC3_PZ_leták_final_en (1).pdf</t>
+          <t>Realizace a vyhodnocení FG_Smlouva bez citlivých údajů.pdf</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2939,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>03.010.03</t>
+          <t>03.010.02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2947,11 +2954,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Realizace a vyhodnocení fokusních skupin</t>
+          <t>Případové studie projektů služeb pro ohrožené děti, rodiny a mladé dospělé v OPZ+</t>
         </is>
       </c>
       <c r="F28" s="2">
-        <v>45184</v>
+        <v>45174</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2965,380 +2972,378 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Realizace a vyhodnocení tematicky zaměřených fokusních skupin
-Zakázka reagovala na nedostatek informací kvalitativního charakteru v řadě výzkumných a implementačních oblastí od přístupu realizátorů projektů v sociální oblasti, přes pohled zástupců samospráv na předškolní péči až po zkušenosti zaměstnavatelů s projekty Úřadu práce ČR. Získané poznatky budou využity pro optimalizaci procesu implementace OPZ+, a také jako doplňující informační zdroj pro lepší zacílení plánovaných výzev či projektů. V neposlední řadě se získané závěry stanou součástí dalších evaluačních výstupů. </t>
+          <t xml:space="preserve">Předmětem plnění veřejné zakázky je terénní šetření spočívající ve zpracování 10 případových studií z 10 vybraných projektů podpořených ve výzvě č. 017 Operačního programu Zaměstnanost Plus (OPZ+) na podporu služeb pro ohrožené děti, rodiny a mladé dospělé. V případě nedostatku relevantních projektů ve výzvě 017 OPZ+ bude počet projektů pro případové studie doplněn z projektů výzvy č. 076 Operačního programu Zaměstnanost (OPZ) na podporu inovativních služeb pro ohrožené děti a rodiny. </t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zakázka přinesla různorodá zjištění v osmi samostatných tematických oblastech.
-Např. v oblasti spolupráce ÚP ČR je jedním ze zjištění, že nestátní neziskové organizace a většina obcí zastoupených v diskuzi považuje spolupráci s ÚP ČR a jeho dotační podporu za klíčový nástroj pro začleňování zranitelných skupin na trh práce a pro jejich sociální integraci. Jako problematický však organizace identifikují zdlouhavý proces vyřizování příspěvků na mzdové náklady podpořených osob, ztížené podmínky jejich včasného plánování, byrokratickou a administrativní zátěž. Řada dalších zjištění, a to rovněž v ostatních tématech, je uvedena v samostatné příloze. </t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Jiná</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>ad-hoc</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Operativní/procesní, Tematická</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTgwOTQ4MTg4NjtQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>Realizace a vyhodnocení FG_Smlouva bez citlivých údajů.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>OP Z</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>03.010.02</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>OP Z  •  Sběr dat pro OPZ</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Sběr dat pro OPZ</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Případové studie projektů služeb pro ohrožené děti, rodiny a mladé dospělé v OPZ+</t>
-        </is>
-      </c>
-      <c r="F29" s="2">
-        <v>45174</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Realizace fokusních skupin a dalších šetření za účelem sběru dat pro OPZ. Výstupy z těchto šetření nejsou samostatnými evaluacemi, ale slouží jako dílčí vstupy pro jiné, komplexní evaluace OPZ nebo jako samostatné analytické podklady.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Předmětem plnění veřejné zakázky je terénní šetření spočívající ve zpracování 10 případových studií z 10 vybraných projektů podpořených ve výzvě č. 017 Operačního programu Zaměstnanost Plus (OPZ+) na podporu služeb pro ohrožené děti, rodiny a mladé dospělé. V případě nedostatku relevantních projektů ve výzvě 017 OPZ+ bude počet projektů pro případové studie doplněn z projektů výzvy č. 076 Operačního programu Zaměstnanost (OPZ) na podporu inovativních služeb pro ohrožené děti a rodiny. </t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
         <is>
           <t xml:space="preserve">Výzkumného šetření se zúčastnilo devět neziskových organizací a jedno město. Uvedené případové studie zachycují komplexní situace projektů a jejich realizátorů z hlediska jejich historie, souvisejících aktivit, vizí do budoucna a využitelnosti financování právě v rámci OPZ+ pro realizaci těchto vizí. Kontext sledovaných případů je dále vystižen ve stručných ?příbězích změny?, které budou podkladem pro další evaluační aktivity v rámci MPSV.
 Pro všechny řešitele z řad neziskových organizací jsou finanční prostředky z ESF klíčovým faktorem jejich rozvoje ? jak odbornosti v oblasti metod sociální práce a profesionalizace řízení, tak šíře poskytovaných služeb a počtu zaměstnanců. Organizace díky evropským projektům mohou poskytovat služby v potřebném rozsahu a především kvalitě, systém standardního financování naopak vede k rigiditě a nižší efektivitě služeb a k neuspokojené poptávce ze strany klientů. Evropské projekty zároveň tvoří zásadní část rozpočtu zkoumaných organizací, neboť standardní financování z krajské úrovně pokrývá maximálně 60 % jejich nákladů. 
 Právě zajištění financování bylo zmiňováno jakožto jedna z hlavních překážek fungování organizací, konkrétně byla zmiňována finanční nestabilita a nízké platy, které neodpovídají kvalifikaci realizátorek a realizátorů projektů. Jakožto další výrazná překážka v činnosti organizací byla zmiňována roztříštěnost systému podpory ohrožených dětí, která snižuje funkčnost jednotlivých služeb. Celkově však bylo nastavení konkrétně výzvy č. 17 OPZ+ hodnoceno řešiteli zkoumaných projektů velmi pozitivně. Mezi pozitivy výzvy byla akcentována zejména velká otevřenost a flexibilita a neomezování podpory jen na úzce vymezené činnosti. Dále byla jako významný klad vnímána dlouhodobost, tedy období realizace delší než jeden rok. </t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>Dopad/výsledky</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>on-going</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Operativní/procesní, Dopadová/Výsledková</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTgwMTE3NzcyOTtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>Smlouva_Případové studie OD_bez citlivých údajů.pdf</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>OP PPR</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>07.012.01</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>OP PPR  •  Evaluace komunikačních aktivit</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Evaluace komunikačních aktivit</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Evaluace komunikačních aktivit</t>
         </is>
       </c>
-      <c r="F30" s="2">
+      <c r="F29" s="2">
         <v>45159</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>v realizaci</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Předmětem evaluace komunikačních aktivit je posouzení efektivity informačních a propagačních opatření prováděných v rámci komunikační strategie (v návaznosti na Společnou komunikační strategii), a to prostřednictvím dotazníkového šetření široké veřejnosti v hl. m. Praze.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">Předmětem je evaluace (kvantitativní výzkum) komunikačních aktivit zadavatele v rámci OP PPR, a to prostřednictvím dotazníkového šetření široké veřejnosti v hl. m. Praze. Předmětem evaluace komunikačních aktivit bude posouzení efektivity informačních a propagačních opatření prováděných v rámci komunikační strategie (v návaznosti na Společnou komunikační strategii).
 Proběhne dotazování přes webové rozhraní, jehož obsahem bude průzkum na cílové skupině minimálně 200 respondentů/1 průzkum ze široké veřejnosti v Praze. Předpokládaný počet opakování sběru dat je 6.
 Respondenti budou dotazováni v přibližně 16 uzavřených a 4 otevřených otázkách (mimo dotazy na osobní údaje) na tyto oblasti (povědomí o OP PPR, povědomí o konkrétních projektech v rámci OP PPR, informační zdroje OP PPR, vnímání přínosu OP PPR a jeho prioritních os, vnímání transparentnosti, zaznamenání komunikačních kampaní, vnímání komunikačních kampaní, ovlivnění názoru apod.). </t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>Ne</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Jiná</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>on-going</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Operativní/procesní</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTY2OTI5MjA1MztQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>Smlouva_přílohy.pdf</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>OP PIK</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>01.026.03</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>OP PIK  •  Ex post evaluace OP PIK a replikace kontrafaktuální dopadové analýzy OP PI</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Ex post evaluace OP PIK a replikace kontrafaktuální dopadové analýzy OP PI</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Situační zpráva OP PIK</t>
         </is>
       </c>
-      <c r="F31" s="2">
+      <c r="F30" s="2">
         <v>45149</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>ukončeno</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Komplexní souhrnná evaluace dopadů Operačního programu Podnikání a inovace pro konkurenceschopnost 2014?2020 (dále též ?OP PIK?) a opětovné kontrafaktuální vyhodnocení dopadů již dříve zpracované evaluace dopadů Operačního programu Podnikání a inovace za období 2007?2013 (déle též ?OP PI?). Primárním účelem je zjištění dopadů podpory poskytované z Evropských strukturálních a investičních fondů na konkurenceschopnost podpořených podniků, a to jak v krátkém (OP PIK), tak ve střednědobém období (OP PI). Na základě vyhodnocení se taktéž očekávají doporučení pro optimalizaci nastavení jednotlivých intervencí ve vztahu k implementaci Operačního programu Technologie a aplikace pro konkurenceschopnost 2021?2027 (dále též ?OP TAK?).</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Syntézy aktuálního stavu dosavadních zjištění, výsledků provedených analýz a návrhů odpovědí na evaluační otázky. Zároveň byla zodpovězena  evaluační otázka týkající se XII. výzvy programu podpory Technologie, která je reakcí na kontrolní akci NKÚ.</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>1) OP PIK podpořil dotacemi projekty v celkové hodnotě převyšující 91 mld. Kč (příspěvek EU) a umožnil schválení úvěrů pro podnikatele ve výši cca 55 mld. Kč. Nejvyšší podpora byla poskytnuta v programech Aplikace, Úspory energie, Inovace, Technologie a Potenciál. Program podpořil celkem 12 712 unikátních podnikatelských subjektů. V drtivé většině (cca 93 %) šlo o malé a střední podniky nebo mikropodniky. Podpora směřuje většinou do zpracovatelského průmyslu, finančními nástroji byly ale výrazně podpořeny také další segmenty ekonomiky, především potom malo- a velkoobchod a také stavebnictví nebo ubytování a pohostinství. Čerpání dotační podpory i finančních nástrojů je regionálně vychýleno směrem k východní části ČR. Nejméně jsou tyto zdroje pro rozvoj podnikání využívány v regionech na severozápadě Čech.
 V rámci finančních nástrojů bylo podnikatelským subjektům schváleno celkem 2139 zvýhodněných úvěrů a poskytnuto 5445 záruk za úvěry u jiných bankovních institucí. Celková výše takto podpořených úvěrů podnikatelských subjektů dosahuje cca 57 mld. Kč. Záruky poskytnuté OP PIK hrály především důležitou roli v bezprostředním řešení negativních dopadů pandemie COVID-19. 
 2) Podpora z XII. výzvy programu Technologie (výzva COVID-19) přispěla ke zvýšení produkce zdravotnického materiálu a produktů, včetně ochranných pomůcek, které byly v pandemické krizi nedostatkové, dlouhodobě ale není udržitelná. Podpora přispěla ke zvládnutí pandemické krize, protože kompenzovala výpadky na jiných trzích. Tento efekt byl ale dočasný. Nepřímým důsledkem podpory je facilitace vstupu na nové trhy.</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>Dopad/výsledky</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>ex-post</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Strategická, Tematická, Dopadová/Výsledková</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkwODUzMjk2ODtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>Zprava IIb - situacni_final.docx</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>OP Z</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>03.011.03</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>OP Z  •  Evaluace výsledků pilotní podpory mezinárodní mobility znevýhodněné mládeže</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Evaluace výsledků pilotní podpory mezinárodní mobility znevýhodněné mládeže</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t xml:space="preserve">Kvalitativní šetření přínosů projektů Mezinárodní mobility </t>
         </is>
       </c>
-      <c r="F32" s="2">
+      <c r="F31" s="2">
         <v>45138</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>ukončeno</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Předmětem evaluace jsou soutěžní výzvy na podporu mezinárodní mobility mládeže v rámci IP 3.1. OPZ (SC 1) Zvýšit kvalitu a kvantitu využívání sociálních inovací a mezinárodní spolupráce v tematických oblastech OPZ. Jedná se o pilotní podporu (testování nového nástroje APZ, úspěšně aplikovaného v Německu, program IDA) zaměřenou na pracovní a sociální integraci znevýhodněných osob do 30 let prostřednictvím stáží u zaměstnavatelů v zahraničí. Cílem je zvýšit pracovní a sociální dovednosti a kompetence účastníků a eliminovat negativní návyky a chování, a tím zlepšit jejich sociální situaci a zvýšit jejich zaměstnanost. 
 Navazující výzva (59) byla vyhlášena v říjnu 2018.  Pro účely evaluace navazující výzvy již od června 2019 probíhá sběr dat formou dotazníků. Data formou dotazníků jsou nastaveny ve formátu tří snímků (před intervencí, během stáže a po ukončení účasti na projektových aktivitách). V roce 2021 byla připravena a vyhlášena veřejná zakázka na kvalitativní došetření výzvy 059.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Předmětem plnění této veřejné zakázky je dílčí kvalitativní šetření, které má vyhodnotit přínosy projektů zaměřených na zvýšení zaměstnanosti a zaměstnatelnosti mladých osob ve věku 15 až 30 let v rámci výzvy číslo 59 OPZ Mezinárodní mobilita a sociální začleňování znevýhodněné mládeže (dále jen "Mezinárodní mobilita mládeže"). Výzva 59 je zacílena na mladé lidi, kteří jsou uchazeči o zaměstnání nebo osoby neaktivní  a zároveň splňují jednu z dalších podmínek uvedených ve výzvě. V roce 2021 byla připravena a vyhlášena veřejná zakázka na kvalitativní došetření výzvy 059. Vstupní zpráva této zakázky byla akceptována na začátku února 2022, průběžná zpráva pak v polovině července 2022. V lednu 2023 byl podepsán Dodatek č. 1 ke Smlouvě, kterým byla v důsledku prodloužení KA šetřených projektů prodloužena také realizace VZ.</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t xml:space="preserve">Z výsledků studie vyplývá, že výzvou definovaná cílová skupina není snadno dosažitelná vzhledem k relativně náročným parametrům (zejména délka evidence na úřadu práce), vzhledem k důsledkům (doznívající) (post)covidové situace (zejména obavy z vycestování) a velmi omezené a často komplikované spolupráci s úřady práce. 
 U projektů výzvy, které byly předmětem šetření této evaluační studie, se jako zcela nejzásadnější ukázal vliv zdravotních omezení účastníků, které ve většině případů přímo souvisely se subjektivními překážkami vstupu na trh práce (nesamostatnost, nedostatečné sebevědomí vč. nízké sebedůvěry, silné, v tomto případě omezující, rodinné vazby apod.), které si často sami účastníci neuvědomují nebo nepřipouštějí. Motivace směrem k práci, resp. získání praxe, získání certifikátu o absolvování zahraniční stáže je pak méně ?přesvědčivá?, méně konkrétní a s až výhledovým, budoucím a spíše potenciálním naplněním. 
 Výsledky studie ukazují, že z pohledu realizátorů jsou nejobtížnější až kritické fáze náboru (obtížné zajištění účastníků, udržování jejich motivace, průběžné doplňování počtu), samotné pracovní stáže v zahraničí (náročná práce mentora, požadavek na jeho univerzální dovedností, s důrazem na praxi v oblasti psychologie) a následná fáze (pokles až propad motivace účastníků po návratu). Ze strany účastníků je jednoznačně nejzásadnější fáze zahraniční stáže (nová situace přinášející pracovní zkušenosti, návyky, sociální vazby, posuny v samostatnosti, sebevědomí, finanční zajištění, kulturní rozhled apod.).   </t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Dopad/výsledky</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>on-going</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Operativní/procesní, Dopadová/Výsledková</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTM5NzI0OTg0NDtQcmlsb2hhRE1TO0ZhbHNl</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Mezinárodní Mobilita_vstupní zpráva_finál.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PRV</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>09.003.14</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PRV  •  Zpracování odpovědí na hodnotící otázky vztažené k prioritním oblastem PRV a technické pomoci PRV</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Zpracování odpovědí na hodnotící otázky vztažené k prioritním oblastem PRV a technické pomoci PRV</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Třináctá zpráva o hodnocení PRV 2014-2020 - březen 2023</t>
+        </is>
+      </c>
+      <c r="F32" s="2">
+        <v>45104</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Zpracování odpovědí na hodnotící otázky pro každou prioritní oblast  zahrnutou v PRV (vč. technické pomoci, Celostátní sítě pro venkov a oblasti, synergií a komplementarit ), vyhodnocení příspěvku PRV k plnění cílů SZP a Strategie EU 2020. Výstupy budou využity jako příprava pro další fáze průběžného hodnocení a ex post hodnocení, zároveň budou sloužit jako podklad pro MMR - NOK k vyhodnocení plnění cílů Dohody o partnerství.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Hodnocení PRV na datech k 31.12.2022.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>viz hodnotící zpráva</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Ano</t>
@@ -3366,48 +3371,53 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Operativní/procesní, Dopadová/Výsledková</t>
+          <t>Strategická, Tematická, Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTM5NzI0OTg0NDtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTgzNDAxNzY3MTtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Mezinárodní Mobilita_vstupní zpráva_finál.pdf</t>
+          <t>230331_PHZ_1_2023_final.pdf</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>https://portal.mze.cz/ssl/web/mze/dotace/program-rozvoje-venkova-na-obdobi-2014/hodnoceni-a-monitoring/hodnoceni/prubezna-zprava-o-hodnoceni-prv-brezen-3.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PRV</t>
+          <t>OP VVV</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>09.003.14</t>
+          <t>02.002.27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PRV  •  Zpracování odpovědí na hodnotící otázky vztažené k prioritním oblastem PRV a technické pomoci PRV</t>
+          <t>OP VVV  •  Průběžná evaluace implementace OP VVV</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Zpracování odpovědí na hodnotící otázky vztažené k prioritním oblastem PRV a technické pomoci PRV</t>
+          <t>Průběžná evaluace implementace OP VVV</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Třináctá zpráva o hodnocení PRV 2014-2020 - březen 2023</t>
+          <t>Průběžná evaluace implementace OP VVV - Závěrečná zpráva</t>
         </is>
       </c>
       <c r="F33" s="2">
-        <v>45104</v>
+        <v>45092</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3416,17 +3426,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Zpracování odpovědí na hodnotící otázky pro každou prioritní oblast  zahrnutou v PRV (vč. technické pomoci, Celostátní sítě pro venkov a oblasti, synergií a komplementarit ), vyhodnocení příspěvku PRV k plnění cílů SZP a Strategie EU 2020. Výstupy budou využity jako příprava pro další fáze průběžného hodnocení a ex post hodnocení, zároveň budou sloužit jako podklad pro MMR - NOK k vyhodnocení plnění cílů Dohody o partnerství.</t>
+          <t>Průběžné hodnocení věcného a finančního pokroku OP VVV + tematická hodnocení (hodnocení prvních výzev, hodnocení S/K vazeb, hodnocení TP, hodnocení multifondovosti, hodnocení horizontálních principů, podklady pro MMR-NOK v roce 2017 a 2019)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Hodnocení PRV na datech k 31.12.2022.</t>
+          <t>summery a podklad pro Shouhrn evaluací programu</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>viz hodnotící zpráva</t>
+          <t>Viz dokument</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3446,7 +3456,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Dopad/výsledky</t>
+          <t>Jiná</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3456,53 +3466,38 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Strategická, Tematická, Dopadová/Výsledková</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTgzNDAxNzY3MTtQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>230331_PHZ_1_2023_final.pdf</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>https://portal.mze.cz/ssl/web/mze/dotace/program-rozvoje-venkova-na-obdobi-2014/hodnoceni-a-monitoring/hodnoceni/prubezna-zprava-o-hodnoceni-prv-brezen-3.html</t>
+          <t>Operativní/procesní</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OP VVV</t>
+          <t>OP D</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>02.002.27</t>
+          <t>04.008.01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OP VVV  •  Průběžná evaluace implementace OP VVV</t>
+          <t xml:space="preserve">OP D  •  Vyhodnocení plnění Komunikačního plánu Operačního programu Doprava v období 2019?2022 </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Průběžná evaluace implementace OP VVV</t>
+          <t xml:space="preserve">Vyhodnocení plnění Komunikačního plánu Operačního programu Doprava v období 2019?2022 </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Průběžná evaluace implementace OP VVV - Závěrečná zpráva</t>
+          <t xml:space="preserve">Vyhodnocení plnění Komunikačního plánu Operačního programu Doprava v období 2019?2022 </t>
         </is>
       </c>
       <c r="F34" s="2">
-        <v>45092</v>
+        <v>45088</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3511,95 +3506,15 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Průběžné hodnocení věcného a finančního pokroku OP VVV + tematická hodnocení (hodnocení prvních výzev, hodnocení S/K vazeb, hodnocení TP, hodnocení multifondovosti, hodnocení horizontálních principů, podklady pro MMR-NOK v roce 2017 a 2019)</t>
+          <t xml:space="preserve">Evaluace komunikačních aktivit s cílem vyhodnotit realizaci komunikačních aktivit OPD v letech 2019 až 2022. Evaluace bude zahrnovat analýzy dostupných průzkumů a realizaci a vyhodnocení dílčích průzkumů na cílových skupinách. </t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>summery a podklad pro Shouhrn evaluací programu</t>
+          <t xml:space="preserve">Evaluace komunikačních aktivit s cílem vyhodnotit realizaci komunikačních aktivit OPD v letech 2019 až 2022. Evaluace bude zahrnovat analýzy dostupných průzkumů a realizaci a vyhodnocení dílčích průzkumů na cílových skupinách. </t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
-        <is>
-          <t>Viz dokument</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Jiná</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>on-going</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Operativní/procesní</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>OP D</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>04.008.01</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OP D  •  Vyhodnocení plnění Komunikačního plánu Operačního programu Doprava v období 2019?2022 </t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vyhodnocení plnění Komunikačního plánu Operačního programu Doprava v období 2019?2022 </t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vyhodnocení plnění Komunikačního plánu Operačního programu Doprava v období 2019?2022 </t>
-        </is>
-      </c>
-      <c r="F35" s="2">
-        <v>45088</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evaluace komunikačních aktivit s cílem vyhodnotit realizaci komunikačních aktivit OPD v letech 2019 až 2022. Evaluace bude zahrnovat analýzy dostupných průzkumů a realizaci a vyhodnocení dílčích průzkumů na cílových skupinách. </t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Evaluace komunikačních aktivit s cílem vyhodnotit realizaci komunikačních aktivit OPD v letech 2019 až 2022. Evaluace bude zahrnovat analýzy dostupných průzkumů a realizaci a vyhodnocení dílčích průzkumů na cílových skupinách. </t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
         <is>
           <t>Evaluátor souhrnně konstatuje, že komunikace OPD v letech 2019 až 2022 probíhala na dostatečné úrovni, která odpovídala cílům stanovených v Ročních komunikačních plánech. Na základě svých expertních znalostí a provedených průzkumech evaluátor identifikoval několik dílčích podnětů, které pomohou k dalšímu zlepšení a rozvoji komunikace řídicího orgánu vůči jeho cílovým skupinám. Řídicí orgán ve sledovaném období zajistil dostatečné a pestré činnosti a aktivity. Podařilo se zrealizovat 92 komunikačních aktivit.
 V České republice je povědomí široké veřejnosti o problematice strukturálních a investičních fondů na poměrně vysoké úrovni. Na druhé straně je z výsledků uvedených v tomto dokumentu patrné, že výsledky se mezi roky 2017 a 2021 v ČR zásadním způsobem již nemění takovým tempem, jak v letech 2010 až 2017. Informovanost o podpoře dopravní infrastruktury je vysoká. Nižší znalost je ve vztahu ke konkrétnímu zdroji financování, což ale evaluátor nepovažuje za nedostatek.
@@ -3607,87 +3522,87 @@
 Odborná veřejnost včetně žadatelů a příjemců se cítí být dostatečně informována. V rámci dostupnosti informací se respondenti z řad cílových skupin odborné veřejnosti shodují na velice malém množství překážek. Z expertního posouzení dvou komunikačních nástrojů ? webu opd.cz a tiskovin vyplývá, že webové stránky www.opd.cz jsou svými uživateli vnímány pozitivně, návštěvnost za dobu jejich existence kontinuálně stoupá. Obsahují tak relevantní a užitečné informace. Pro tiskoviny byla vhodně zvolena témata vzhledem k charakteru sdělení. Tiskoviny o OPD jsou zpracovány v jednoduchém a pochopitelném textu. Řídicí orgán OPD plnil plánované indikátory stanovené v Ročních komunikačních plánech i přes situaci způsobenou nouzovým stavem na území České republiky.</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>Jiná</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>publicita</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>ex-post</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Tematická</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTgxMzcwMzgwNTtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>Tabulka hlavních závěrů a doporučení.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>NOK (MMR)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>NOK.002.10</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>NOK (MMR)  •  Vyhodnocení komunikačních aktivit NOK</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Vyhodnocení komunikačních aktivit NOK</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Hodnocení povědomí veřejnosti o problematice fondů EU 2023-Jaro 2023</t>
         </is>
       </c>
-      <c r="F36" s="2">
+      <c r="F35" s="2">
         <v>45070</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>ukončeno</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Kvalitativní vyhodnocení komunikačních aktivit Národního orgánu pro koordinaci zrealizovaných za dané období. Výsledky budou použity pro nastavení další komunikační strategie v navazujících ročních komunikačních plánech.
 Předmětem hodnocení:
@@ -3696,12 +3611,12 @@
 ? průběžná kontrola naplňování cílových hodnot indikátorů stanovených ve Společné komunikační strategii 2014?2020 v oblasti komunikace fondů EU (Míra informovanosti o fondech EU u cílové skupiny; Míra znalosti podpořených projektů u cílové skupiny; Míra povědomí široké veřejnosti o fondech EU).</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Cílem hodnocení bylo zjistit aktuální povědomí široké veřejnosti o problematice fondů EU v roce 2023 před spuštěním komunikační kampaně. Šetření ukázalo, že fondy EU znají 3/4 dotázaných. Polovina dotázaných má k fondům EU pozitivní postoj, 37 % má postoj neutrální.</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Členství ČR v EU vnímá pozitivně 43 % dotázaných ("příznivci"), opačný názor má 12 % ("odpůrci). Neutrální vztah nebo žádný názor má 45 % respondentů. Od roku 2021 mírně přibylo příznivců a výrazně ubylo odpůrců.
 Informace o fondech EU vnímá jako dostupné 29 % dotázaných. Od šetření v roce 2021 nedošlo v tomto ohledu ke změně. Konkrétní projekt financovaný z fondů EU si vybaví 53 % dotázaných, oproti minulému šetření jde o mírný nárůst. Přínosy evropských fondů jsou vnímány nadpoloviční většinou respondentů pozitivně. Existuje silný vztah mezi znalostí projektu a vnímáním osobního přínosu. Důvěra v transparentnost procesu rozdělování zdrojů z fondů EU částečně posílila.
@@ -3709,6 +3624,101 @@
 Hodnocení bylo provedeno metodou CAWI na široké veřejnosti (nikoliv internetové, jak tomu bylo ve většině předchozích šetření), a to na rovnoměrně rozloženém vzorku obyvatel (15+ let) po celé České republice dle územních jednotek NUTS II, pohlaví, věku, vzdělání a velikosti obce.</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Dopad/výsledky</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>publicita</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>on-going</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Tematická, Dopadová/Výsledková</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTgwNTA0NjkxODtQcmlsb2hhRE1TO0ZhbHNl</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Povědomí o fondech EU_jaro 2023.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>OP PIK</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>01.026.02</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>OP PIK  •  Ex post evaluace OP PIK a replikace kontrafaktuální dopadové analýzy OP PI</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ex post evaluace OP PIK a replikace kontrafaktuální dopadové analýzy OP PI</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Kontrafaktuální dopadová analýza OP PI</t>
+        </is>
+      </c>
+      <c r="F36" s="2">
+        <v>45051</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Komplexní souhrnná evaluace dopadů Operačního programu Podnikání a inovace pro konkurenceschopnost 2014?2020 (dále též ?OP PIK?) a opětovné kontrafaktuální vyhodnocení dopadů již dříve zpracované evaluace dopadů Operačního programu Podnikání a inovace za období 2007?2013 (déle též ?OP PI?). Primárním účelem je zjištění dopadů podpory poskytované z Evropských strukturálních a investičních fondů na konkurenceschopnost podpořených podniků, a to jak v krátkém (OP PIK), tak ve střednědobém období (OP PI). Na základě vyhodnocení se taktéž očekávají doporučení pro optimalizaci nastavení jednotlivých intervencí ve vztahu k implementaci Operačního programu Technologie a aplikace pro konkurenceschopnost 2021?2027 (dále též ?OP TAK?).</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Replikace kontrafaktuální dopadové analýzy OP PI, během níž byla dodržena metodologie původní kontrafaktuální dopadové analýzy provedené v rámci Ex post OP PI.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Vzhledem k tomu, že jako relevantní ukazatele konkurenceschopnosti podniků jsou obecně považovány ukazatele založené na přidané hodnotě a tržbách, produktivitě a rentabilitě podniků, je vliv podpory na konkurenceschopnost podpořených podniků hodnocen i ve střednědobém horizontu nadále jako nejednoznačný. I když analýza potvrdila pozitivní efekt realizace podpory v řadě ukazatelů, v zásadních indikátorech konkurenceschopnosti nebyly pozorovány významné rozdíly v podnicích podpořených ve srovnání s podniky nepodpořenými. Celkově tedy realizace podpory z OP PI neměla statisticky významný dopad na konkurenceschopnost podpořených podniků ve sledovaném střednědobém období po ukončení programu. Pozitivní dopad podpory OP PI na tržby a přidanou hodnotu podniků lze pozorovat spíše ojediněle. V řadě programů podpory měla podpora pozitivní vliv na zaměstnanost. Nejvýraznějším dopadem podpory je zvýšení hodnoty hmotného investičního majetku, podpora má také pozitivní vliv na strukturu a zdroje financování. Výsledky kontrafaktuální analýzy naznačují ale také některé negativní dopady na podpořený podniky, jako je zhoršení hospodárnosti a rentability.</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>Ano</t>
@@ -3729,60 +3739,55 @@
           <t>Dopad/výsledky</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>publicita</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>on-going</t>
+          <t>ex-post</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Tematická, Dopadová/Výsledková</t>
+          <t>Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTgwNTA0NjkxODtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkwODUyNTE1MTtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Povědomí o fondech EU_jaro 2023.pdf</t>
+          <t>Zprava IIa - CIE OPPI_v2.docx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OP PIK</t>
+          <t>OP D</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01.026.02</t>
+          <t>04.007.01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OP PIK  •  Ex post evaluace OP PIK a replikace kontrafaktuální dopadové analýzy OP PI</t>
+          <t>OP D  •  Hodnocení vlivu Operačního programu Doprava 2014 - 2020 na rozvoj vybraných aglomerací</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ex post evaluace OP PIK a replikace kontrafaktuální dopadové analýzy OP PI</t>
+          <t>Hodnocení vlivu Operačního programu Doprava 2014 - 2020 na rozvoj vybraných aglomerací</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kontrafaktuální dopadová analýza OP PI</t>
+          <t>Hodnocení vlivu Operačního programu Doprava 2014 - 2020 na rozvoj vybraných aglomerací</t>
         </is>
       </c>
       <c r="F37" s="2">
-        <v>45051</v>
+        <v>45031</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3791,17 +3796,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Komplexní souhrnná evaluace dopadů Operačního programu Podnikání a inovace pro konkurenceschopnost 2014?2020 (dále též ?OP PIK?) a opětovné kontrafaktuální vyhodnocení dopadů již dříve zpracované evaluace dopadů Operačního programu Podnikání a inovace za období 2007?2013 (déle též ?OP PI?). Primárním účelem je zjištění dopadů podpory poskytované z Evropských strukturálních a investičních fondů na konkurenceschopnost podpořených podniků, a to jak v krátkém (OP PIK), tak ve střednědobém období (OP PI). Na základě vyhodnocení se taktéž očekávají doporučení pro optimalizaci nastavení jednotlivých intervencí ve vztahu k implementaci Operačního programu Technologie a aplikace pro konkurenceschopnost 2021?2027 (dále též ?OP TAK?).</t>
+          <t xml:space="preserve">Vyhodnocení výsledků/přínosů vybraných projektů Operačního programu Doprava 2014 ? 2020 (dále jen ?OPD2?) zaměřených na udržitelnou a bezpečnou dopravu ve vybraných aglomeracích. Vybranými aglomeracemi budou Brněnská metropolitní oblast, Olomoucká aglomerace, Hradecko ? pardubická aglomerace, Plzeňská aglomerace a Jihlavská aglomerace. Součástí díla bude grafická vizualizace výsledků/dopadů  projektů OPD2 do jednotlivých vybraných aglomerací a návrh pro hodnocení projektů Operačního programu Doprava 2021 ? 2027.  Cílem evaluace je posouzení, jak podpora z Evropských strukturálních a investičních fondů přispěla k dosahování stanovených cílů OPD2, včetně hodnocení 3E  na úrovni jednotlivých vybraných specifických cílů OPD2 a jaký vliv mají projekty OPD2 na rozvoj vybraných aglomerací. </t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Replikace kontrafaktuální dopadové analýzy OP PI, během níž byla dodržena metodologie původní kontrafaktuální dopadové analýzy provedené v rámci Ex post OP PI.</t>
+          <t>Vyhodnocení výsledků/přínosů vybraných projektů Operačního programu Doprava 2014 ? 2020 (dále jen ?OPD2?) zaměřených na udržitelnou a bezpečnou dopravu ve vybraných aglomeracích. Vybranými aglomeracemi budou Brněnská metropolitní oblast, Olomoucká aglomerace, Hradecko ? pardubická aglomerace, Plzeňská aglomerace a Jihlavská aglomerace. Součástí díla bude grafická vizualizace výsledků/dopadů  projektů OPD2 do jednotlivých vybraných aglomerací a návrh pro hodnocení projektů Operačního programu Doprava 2021 ? 2027.  Cílem evaluace je posouzení, jak podpora z Evropských strukturálních a investičních fondů přispěla k dosahování stanovených cílů OPD2, včetně hodnocení 3E  na úrovni jednotlivých vybraných specifických cílů OPD2 a jaký vliv mají projekty OPD2 na rozvoj vybraných aglomerací.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Vzhledem k tomu, že jako relevantní ukazatele konkurenceschopnosti podniků jsou obecně považovány ukazatele založené na přidané hodnotě a tržbách, produktivitě a rentabilitě podniků, je vliv podpory na konkurenceschopnost podpořených podniků hodnocen i ve střednědobém horizontu nadále jako nejednoznačný. I když analýza potvrdila pozitivní efekt realizace podpory v řadě ukazatelů, v zásadních indikátorech konkurenceschopnosti nebyly pozorovány významné rozdíly v podnicích podpořených ve srovnání s podniky nepodpořenými. Celkově tedy realizace podpory z OP PI neměla statisticky významný dopad na konkurenceschopnost podpořených podniků ve sledovaném střednědobém období po ukončení programu. Pozitivní dopad podpory OP PI na tržby a přidanou hodnotu podniků lze pozorovat spíše ojediněle. V řadě programů podpory měla podpora pozitivní vliv na zaměstnanost. Nejvýraznějším dopadem podpory je zvýšení hodnoty hmotného investičního majetku, podpora má také pozitivní vliv na strukturu a zdroje financování. Výsledky kontrafaktuální analýzy naznačují ale také některé negativní dopady na podpořený podniky, jako je zhoršení hospodárnosti a rentability.</t>
+          <t xml:space="preserve">Souhrnně lze říci, že projekty z OPD2 přinesly řadu pozitivních aspektů do fungování dopravy v aglomeracích. Mezi ty nejpodstatnější patří úspory času při využívání různých druhů dopravy, zlepšení dopravní situace v aglomeraci a zvýšení atraktivity veřejné dopravy.                                                                                                   Hodnocené projekty obecně přispívají k většímu využívání železnice a městské hromadné dopravy v aglomeracích. Dosahují toho jednak úsporou cestovního času cestujících, tak i snižováním bariér při nástupu a výstupu, zlepšováním přestupních vazeb a zlepšováním informačních systémů. Dynamické informační prvky s aktuálními odjezdy spojů v MHD se stávají standardem. V aglomeracích, kde byly zavedeny inteligentní dopravní systémy, došlo v naprosté většině k posílení bezpečnosti na silnicích.   Všechny projekty, které bylo možné posoudit, přinesly dohromady roční časovou úsporu ve výši 14 916 643 hodin cestovního času. V průměru na jeden projekt jde o úsporu o velikosti 262 tis. hodin času.   Na základě semikvantitativního hodnocení bylo zjištěno, že reálně má pozitivní vliv na kvalitu ovzduší prokazatelně jen třetina (33 %) projektů, naprostá většina ostatních (60 %) má na ovzduší vliv nulový či nevýznamný.  Z hodnocení dopadů na hlukovou zátěž vyplývá, že reálně má vliv na menší hlukovou zátěž 33 % projektů (26), negativní vliv na hlukovou zátěž se dá prokázat u 4 % projektů (3). Až u 54 % projektů (42) nejsou k dispozici dostatečná data k vyhodnocení.                                                                                                                                                                                                      </t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3824,6 +3829,11 @@
           <t>Dopad/výsledky</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>plnění cílů</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>ex-post</t>
@@ -3831,48 +3841,48 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Dopadová/Výsledková</t>
+          <t>Strategická, Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkwODUyNTE1MTtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTcxODMzOTEwNjtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Zprava IIa - CIE OPPI_v2.docx</t>
+          <t>Smlouva o dílo.pdf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OP D</t>
+          <t>OP VVV</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>04.007.01</t>
+          <t>02.011.16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OP D  •  Hodnocení vlivu Operačního programu Doprava 2014 - 2020 na rozvoj vybraných aglomerací</t>
+          <t>OP VVV  •  Evaluace IPs PO3 OP VVV - II.: (APIV A, APIV B, KSH, MOV, PPUČ)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Hodnocení vlivu Operačního programu Doprava 2014 - 2020 na rozvoj vybraných aglomerací</t>
+          <t>Evaluace IPs PO3 OP VVV - II.: (APIV A, APIV B, KSH, MOV, PPUČ)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hodnocení vlivu Operačního programu Doprava 2014 - 2020 na rozvoj vybraných aglomerací</t>
+          <t>Evaluace projektu Komplexní systém hodnocení (KSH): Závěrečná zpráva 2022</t>
         </is>
       </c>
       <c r="F38" s="2">
-        <v>45031</v>
+        <v>45015</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3881,17 +3891,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vyhodnocení výsledků/přínosů vybraných projektů Operačního programu Doprava 2014 ? 2020 (dále jen ?OPD2?) zaměřených na udržitelnou a bezpečnou dopravu ve vybraných aglomeracích. Vybranými aglomeracemi budou Brněnská metropolitní oblast, Olomoucká aglomerace, Hradecko ? pardubická aglomerace, Plzeňská aglomerace a Jihlavská aglomerace. Součástí díla bude grafická vizualizace výsledků/dopadů  projektů OPD2 do jednotlivých vybraných aglomerací a návrh pro hodnocení projektů Operačního programu Doprava 2021 ? 2027.  Cílem evaluace je posouzení, jak podpora z Evropských strukturálních a investičních fondů přispěla k dosahování stanovených cílů OPD2, včetně hodnocení 3E  na úrovni jednotlivých vybraných specifických cílů OPD2 a jaký vliv mají projekty OPD2 na rozvoj vybraných aglomerací. </t>
+          <t>Průběžné hodnocení projektů APIV A, APIV B, KSH, MOV, PPUČ</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Vyhodnocení výsledků/přínosů vybraných projektů Operačního programu Doprava 2014 ? 2020 (dále jen ?OPD2?) zaměřených na udržitelnou a bezpečnou dopravu ve vybraných aglomeracích. Vybranými aglomeracemi budou Brněnská metropolitní oblast, Olomoucká aglomerace, Hradecko ? pardubická aglomerace, Plzeňská aglomerace a Jihlavská aglomerace. Součástí díla bude grafická vizualizace výsledků/dopadů  projektů OPD2 do jednotlivých vybraných aglomerací a návrh pro hodnocení projektů Operačního programu Doprava 2021 ? 2027.  Cílem evaluace je posouzení, jak podpora z Evropských strukturálních a investičních fondů přispěla k dosahování stanovených cílů OPD2, včetně hodnocení 3E  na úrovni jednotlivých vybraných specifických cílů OPD2 a jaký vliv mají projekty OPD2 na rozvoj vybraných aglomerací.</t>
+          <t>Závěrečná zpráva projektu KSH</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Souhrnně lze říci, že projekty z OPD2 přinesly řadu pozitivních aspektů do fungování dopravy v aglomeracích. Mezi ty nejpodstatnější patří úspory času při využívání různých druhů dopravy, zlepšení dopravní situace v aglomeraci a zvýšení atraktivity veřejné dopravy.                                                                                                   Hodnocené projekty obecně přispívají k většímu využívání železnice a městské hromadné dopravy v aglomeracích. Dosahují toho jednak úsporou cestovního času cestujících, tak i snižováním bariér při nástupu a výstupu, zlepšováním přestupních vazeb a zlepšováním informačních systémů. Dynamické informační prvky s aktuálními odjezdy spojů v MHD se stávají standardem. V aglomeracích, kde byly zavedeny inteligentní dopravní systémy, došlo v naprosté většině k posílení bezpečnosti na silnicích.   Všechny projekty, které bylo možné posoudit, přinesly dohromady roční časovou úsporu ve výši 14 916 643 hodin cestovního času. V průměru na jeden projekt jde o úsporu o velikosti 262 tis. hodin času.   Na základě semikvantitativního hodnocení bylo zjištěno, že reálně má pozitivní vliv na kvalitu ovzduší prokazatelně jen třetina (33 %) projektů, naprostá většina ostatních (60 %) má na ovzduší vliv nulový či nevýznamný.  Z hodnocení dopadů na hlukovou zátěž vyplývá, že reálně má vliv na menší hlukovou zátěž 33 % projektů (26), negativní vliv na hlukovou zátěž se dá prokázat u 4 % projektů (3). Až u 54 % projektů (42) nejsou k dispozici dostatečná data k vyhodnocení.                                                                                                                                                                                                      </t>
+          <t>Projektové cíle a očekávané přínosy projektu lze označit za naplněné. Výstupy a výsledky dosažené v rámci projektu se prokázaly jako užitečné a uplatnitelné v praxi a naplňují tak veškerý potenciál pro to, aby v dlouhodobém horizontu přinesly kýžené změny do vzdělávacího systému. Inspekční pracovníci, vedení škol a pedagogové a další aktéři ve vzdělávání mají k dispozici nástroje, které si dal projekt za cíl přinést.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3921,22 +3931,22 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>ex-post</t>
+          <t>on-going</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Strategická, Dopadová/Výsledková</t>
+          <t>Strategická, Operativní/procesní, Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTcxODMzOTEwNjtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7NjA0NjE2NzQ0O1ByaWxvaGFETVM7RmFsc2U=</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Smlouva o dílo.pdf</t>
+          <t>Závěrečná_zpráva_Evaluace_IPs_II_KSH.pdf</t>
         </is>
       </c>
     </row>
@@ -3948,26 +3958,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>02.011.16</t>
+          <t>02.002.14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>OP VVV  •  Evaluace IPs PO3 OP VVV - II.: (APIV A, APIV B, KSH, MOV, PPUČ)</t>
+          <t>OP VVV  •  Průběžná evaluace implementace OP VVV</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Evaluace IPs PO3 OP VVV - II.: (APIV A, APIV B, KSH, MOV, PPUČ)</t>
+          <t>Průběžná evaluace implementace OP VVV</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Evaluace projektu Komplexní systém hodnocení (KSH): Závěrečná zpráva 2022</t>
+          <t>Průběžná evaluace implementace OP VVV - Průběžná zpráva k 15. 3. 2023</t>
         </is>
       </c>
       <c r="F39" s="2">
-        <v>45015</v>
+        <v>45000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3976,17 +3986,17 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Průběžné hodnocení projektů APIV A, APIV B, KSH, MOV, PPUČ</t>
+          <t>Průběžné hodnocení věcného a finančního pokroku OP VVV + tematická hodnocení (hodnocení prvních výzev, hodnocení S/K vazeb, hodnocení TP, hodnocení multifondovosti, hodnocení horizontálních principů, podklady pro MMR-NOK v roce 2017 a 2019)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Závěrečná zpráva projektu KSH</t>
+          <t>vyhodnocení věcného a finančního pokroku a celkového řízení programu + hodnocení vazby intervencí programu k relevantním strategiím, koncepcím a dalším dokumentům + ostatní aspekty</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Projektové cíle a očekávané přínosy projektu lze označit za naplněné. Výstupy a výsledky dosažené v rámci projektu se prokázaly jako užitečné a uplatnitelné v praxi a naplňují tak veškerý potenciál pro to, aby v dlouhodobém horizontu přinesly kýžené změny do vzdělávacího systému. Inspekční pracovníci, vedení škol a pedagogové a další aktéři ve vzdělávání mají k dispozici nástroje, které si dal projekt za cíl přinést.</t>
+          <t>Viz dokument</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4006,7 +4016,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Dopad/výsledky</t>
+          <t>Jiná</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4021,17 +4031,17 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Strategická, Operativní/procesní, Dopadová/Výsledková</t>
+          <t>Operativní/procesní</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7NjA0NjE2NzQ0O1ByaWxvaGFETVM7RmFsc2U=</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODE0MTY1NDE7UHJpbG9oYURNUztGYWxzZQ==</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Závěrečná_zpráva_Evaluace_IPs_II_KSH.pdf</t>
+          <t>MSMT_Prubezna evaluace_Prubezna zprava 14_reg.škol_FINAL.pdf</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4053,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>02.002.14</t>
+          <t>02.002.24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4058,15 +4068,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Průběžná evaluace implementace OP VVV - Průběžná zpráva k 15. 3. 2023</t>
+          <t>3. Hodnocení naplňování horizontálních principů v rámci implementace OP VVV</t>
         </is>
       </c>
       <c r="F40" s="2">
-        <v>45000</v>
+        <v>44941</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ukončeno</t>
+          <t>plánováno</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4075,101 +4085,6 @@
         </is>
       </c>
       <c r="I40" t="inlineStr">
-        <is>
-          <t>vyhodnocení věcného a finančního pokroku a celkového řízení programu + hodnocení vazby intervencí programu k relevantním strategiím, koncepcím a dalším dokumentům + ostatní aspekty</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Viz dokument</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Jiná</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>plnění cílů</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>on-going</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Operativní/procesní</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODE0MTY1NDE7UHJpbG9oYURNUztGYWxzZQ==</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>MSMT_Prubezna evaluace_Prubezna zprava 14_reg.škol_FINAL.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>OP VVV</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>02.002.24</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>OP VVV  •  Průběžná evaluace implementace OP VVV</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Průběžná evaluace implementace OP VVV</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>3. Hodnocení naplňování horizontálních principů v rámci implementace OP VVV</t>
-        </is>
-      </c>
-      <c r="F41" s="2">
-        <v>44941</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>plánováno</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Průběžné hodnocení věcného a finančního pokroku OP VVV + tematická hodnocení (hodnocení prvních výzev, hodnocení S/K vazeb, hodnocení TP, hodnocení multifondovosti, hodnocení horizontálních principů, podklady pro MMR-NOK v roce 2017 a 2019)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
         <is>
           <t>Hodnocení míry příspěvku intervencí OP VVV k horizontálním principům, konkrétně:
 - podpoře rovnosti žen a mužů,
@@ -4178,9 +4093,99 @@
 a to v souladu s informacemi definovanými v kapitole 11 Horizontální principy programového dokumentu OP VVV?</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>viz dokument</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Jiná</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>on-going</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Operativní/procesní</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODE1MTE4Nzk7UHJpbG9oYURNUztGYWxzZQ==</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>MEYS_Ongoing evaluation_HP_2022_ex summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>OP VVV</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>02.002.26</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>OP VVV  •  Průběžná evaluace implementace OP VVV</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Průběžná evaluace implementace OP VVV</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2. Hodnocení aktivit a výsledků Technické pomoci OP VVV</t>
+        </is>
+      </c>
+      <c r="F41" s="2">
+        <v>44941</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Průběžné hodnocení věcného a finančního pokroku OP VVV + tematická hodnocení (hodnocení prvních výzev, hodnocení S/K vazeb, hodnocení TP, hodnocení multifondovosti, hodnocení horizontálních principů, podklady pro MMR-NOK v roce 2017 a 2019)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Jaká je efektivita realizace podporovaných aktivit při dosahování specifických cílů a definovaných výsledků Technické pomoci OP VVV?</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>viz dokument</t>
+          <t>Viz dokument</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4215,43 +4220,43 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODE1MTE4Nzk7UHJpbG9oYURNUztGYWxzZQ==</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODE1MTIwMjY7UHJpbG9oYURNUztGYWxzZQ==</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>MEYS_Ongoing evaluation_HP_2022_ex summary.pdf</t>
+          <t>MSMT_Prubezna evaluace_TP 2022_Man shrnuti.pdf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>OP VVV</t>
+          <t>OP PIK</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>02.002.26</t>
+          <t>01.025.02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OP VVV  •  Průběžná evaluace implementace OP VVV</t>
+          <t>OP PIK  •  Vyhodnocení programu podpory Inovační vouchery OP PIK</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Průběžná evaluace implementace OP VVV</t>
+          <t>Vyhodnocení programu podpory Inovační vouchery OP PIK</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2. Hodnocení aktivit a výsledků Technické pomoci OP VVV</t>
+          <t>Vyhodnocení programu podpory Inovační vouchery OP PIK: Závěrečná zpráva</t>
         </is>
       </c>
       <c r="F42" s="2">
-        <v>44941</v>
+        <v>44936</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4260,17 +4265,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Průběžné hodnocení věcného a finančního pokroku OP VVV + tematická hodnocení (hodnocení prvních výzev, hodnocení S/K vazeb, hodnocení TP, hodnocení multifondovosti, hodnocení horizontálních principů, podklady pro MMR-NOK v roce 2017 a 2019)</t>
+          <t>Předmětem veřejné zakázky je vyhodnocení programu podpory Inovační vouchery OP PIK. Bude zanalyzováno oborové členění podpořených podniků, proveden přehled poskytovatelů služeb podle jejich typů, vyhodnocen vztah mezi příjemcem podpory a poskytovatelem služeb, včetně teritoriálních vazeb a následných společných projektů, v neposlední řadě bude zjištěn podíl projektů s ekonomickými přínosy.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Jaká je efektivita realizace podporovaných aktivit při dosahování specifických cílů a definovaných výsledků Technické pomoci OP VVV?</t>
+          <t>Předmětem Závěrečné zprávy je vyhodnocení programu podpory Inovační vouchery OP PIK. Bylo zanalyzováno oborové členění podpořených podniků, proveden přehled poskytovatelů služeb podle jejich typů, vyhodnocen vztah mezi příjemcem podpory a poskytovatelem služeb, včetně teritoriálních vazeb a následných společných projektů a v neposlední řadě bude zjištěn podíl projektů s ekonomickými přínosy.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Viz dokument</t>
+          <t>Projekty Inovačních voucherů OP PIK významně přispívají k vytváření spolupráce mezi MSP a organizacemi pro výzkum a šíření znalostí, vedou ke zlepšení produkce a zvýšení zisku podpořených podniků.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4290,58 +4295,58 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Jiná</t>
+          <t>Dopad/výsledky</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>on-going</t>
+          <t>ad-hoc</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Operativní/procesní</t>
+          <t>Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODE1MTIwMjY7UHJpbG9oYURNUztGYWxzZQ==</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTY1Njc0MDc1NDtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>MSMT_Prubezna evaluace_TP 2022_Man shrnuti.pdf</t>
+          <t>VIV ZZ Informační leták.pdf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OP PIK</t>
+          <t>NOK (MMR)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01.025.02</t>
+          <t>NOK.003.07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OP PIK  •  Vyhodnocení programu podpory Inovační vouchery OP PIK</t>
+          <t>NOK (MMR)  •  Hodnocení plnění cílů Koncepce JMP</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Vyhodnocení programu podpory Inovační vouchery OP PIK</t>
+          <t>Hodnocení plnění cílů Koncepce JMP</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vyhodnocení programu podpory Inovační vouchery OP PIK: Závěrečná zpráva</t>
+          <t>Hodnocení reflexe doporučení k jednotnému metodickému prostředí do jednotného národního rámce pro programové období 2021-2027</t>
         </is>
       </c>
       <c r="F43" s="2">
-        <v>44936</v>
+        <v>44930</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -4349,96 +4354,6 @@
         </is>
       </c>
       <c r="H43" t="inlineStr">
-        <is>
-          <t>Předmětem veřejné zakázky je vyhodnocení programu podpory Inovační vouchery OP PIK. Bude zanalyzováno oborové členění podpořených podniků, proveden přehled poskytovatelů služeb podle jejich typů, vyhodnocen vztah mezi příjemcem podpory a poskytovatelem služeb, včetně teritoriálních vazeb a následných společných projektů, v neposlední řadě bude zjištěn podíl projektů s ekonomickými přínosy.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Předmětem Závěrečné zprávy je vyhodnocení programu podpory Inovační vouchery OP PIK. Bylo zanalyzováno oborové členění podpořených podniků, proveden přehled poskytovatelů služeb podle jejich typů, vyhodnocen vztah mezi příjemcem podpory a poskytovatelem služeb, včetně teritoriálních vazeb a následných společných projektů a v neposlední řadě bude zjištěn podíl projektů s ekonomickými přínosy.</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Projekty Inovačních voucherů OP PIK významně přispívají k vytváření spolupráce mezi MSP a organizacemi pro výzkum a šíření znalostí, vedou ke zlepšení produkce a zvýšení zisku podpořených podniků.</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Dopad/výsledky</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>ad-hoc</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Dopadová/Výsledková</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTY1Njc0MDc1NDtQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>VIV ZZ Informační leták.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>NOK (MMR)</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>NOK.003.07</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>NOK (MMR)  •  Hodnocení plnění cílů Koncepce JMP</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Hodnocení plnění cílů Koncepce JMP</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Hodnocení reflexe doporučení k jednotnému metodickému prostředí do jednotného národního rámce pro programové období 2021-2027</t>
-        </is>
-      </c>
-      <c r="F44" s="2">
-        <v>44930</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
         <is>
           <t>Zhodnocení stavu plnění cílů Koncepce jednotného metodického prostředí (JMP). Vyhodnocení zjednodušení procesů a postupů, příspěvku elektronizace procesů k ulehčení administrativních procesů a protikorupčních prvků v návaznosti na implementaci Strategie boje s podvody a korupcí (Strategie) do JMP.
 Hodnocení je zpětnou vazbou pro MMR-NOK v oblasti nastavování pravidel a procesů popsaných v Koncepci JMP. Na základě identifikace procesů, které způsobují nadbytečnou administrativní zátěž, budou definovány doporučení pro změnu nastavení pravidel a postupů JMP. Bude zkoumáno, zda a jak jednotlivé procesy fungují, důvody případné nefunkčnosti a navrženy změny pro jejich optimalizaci.
@@ -4448,14 +4363,109 @@
 - zhodnocení vybraných procesů, které zjednodušují implementaci a administraci (jak na úrovni příjemců, tak ŘO).</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Cílem hodnocení bylo posouzení, zda určené metodické pokyny spadající do Jednotného národního rámce (JNR, 2021-2027) reflektují všechna vhodná doporučení a podněty, jež vzešly zejména z hodnocení týkajících se jednotného metodického prostředí (JMP, 2014-2020) a z veřejných i neveřejných konzultací.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Evaluace prokázala, že do metodického prostředí pro programové období 2021-2027 byla promítnuta většina relevantních doporučení odrážejících zkušenosti z předchozí implementace fondů EU. Metodické prostředí prošlo od minulého programového období významnou pozitivní změnou. Nová metodická úprava nastavuje potřebný metodický rámec, ale zohledňuje i specifické potřeby subjektů implementační struktury. Většina doporučení z analyzovaných evaluací a veřejných i neveřejných konzultací byla do JNR zapracována v dostatečné míře. V případě, že některá doporučení nebyla zohledněna, je jejich nezapracování odůvodnitelné. Do budoucna nelze vyloučit případné další úpravy a optimalizaci JNR v závislosti na potřeby plynoucí z řízení a koordinace Dohody o partnerství.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Jiná</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>řízení a implementace</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>ad-hoc</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Operativní/procesní</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTc0MDcwMjI3MTtQcmlsb2hhRE1TO0ZhbHNl</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Závěrečná prezentace_Reflexe doporučení k JMP do JNR.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>OP PIK</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>01.026.01</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>OP PIK  •  Ex post evaluace OP PIK a replikace kontrafaktuální dopadové analýzy OP PI</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Ex post evaluace OP PIK a replikace kontrafaktuální dopadové analýzy OP PI</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Vstupní zpráva</t>
+        </is>
+      </c>
+      <c r="F44" s="2">
+        <v>44929</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Komplexní souhrnná evaluace dopadů Operačního programu Podnikání a inovace pro konkurenceschopnost 2014?2020 (dále též ?OP PIK?) a opětovné kontrafaktuální vyhodnocení dopadů již dříve zpracované evaluace dopadů Operačního programu Podnikání a inovace za období 2007?2013 (déle též ?OP PI?). Primárním účelem je zjištění dopadů podpory poskytované z Evropských strukturálních a investičních fondů na konkurenceschopnost podpořených podniků, a to jak v krátkém (OP PIK), tak ve střednědobém období (OP PI). Na základě vyhodnocení se taktéž očekávají doporučení pro optimalizaci nastavení jednotlivých intervencí ve vztahu k implementaci Operačního programu Technologie a aplikace pro konkurenceschopnost 2021?2027 (dále též ?OP TAK?).</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Cílem hodnocení bylo posouzení, zda určené metodické pokyny spadající do Jednotného národního rámce (JNR, 2021-2027) reflektují všechna vhodná doporučení a podněty, jež vzešly zejména z hodnocení týkajících se jednotného metodického prostředí (JMP, 2014-2020) a z veřejných i neveřejných konzultací.</t>
+          <t>Obsahuje zejména metodický přístup k řešení evaluačních otázek, souhrn dosavadního zjištění a soubor z nich plynoucích hypotéz. Vstupní zpráva rovněž obsahuje závazný harmonogram plnění projektu, včetně stanovení termínů realizace terénních šetření a specifikace lhůt pro případnou součinnost ze strany zadavatele.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Evaluace prokázala, že do metodického prostředí pro programové období 2021-2027 byla promítnuta většina relevantních doporučení odrážejících zkušenosti z předchozí implementace fondů EU. Metodické prostředí prošlo od minulého programového období významnou pozitivní změnou. Nová metodická úprava nastavuje potřebný metodický rámec, ale zohledňuje i specifické potřeby subjektů implementační struktury. Většina doporučení z analyzovaných evaluací a veřejných i neveřejných konzultací byla do JNR zapracována v dostatečné míře. V případě, že některá doporučení nebyla zohledněna, je jejich nezapracování odůvodnitelné. Do budoucna nelze vyloučit případné další úpravy a optimalizaci JNR v závislosti na potřeby plynoucí z řízení a koordinace Dohody o partnerství.</t>
+          <t>Nerelevantní pro tuto etapu</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4475,63 +4485,58 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Jiná</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>řízení a implementace</t>
+          <t>Dopad/výsledky</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>ad-hoc</t>
+          <t>ex-post</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Operativní/procesní</t>
+          <t>Strategická, Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTc0MDcwMjI3MTtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkwODUxOTQwMztQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Závěrečná prezentace_Reflexe doporučení k JMP do JNR.pdf</t>
+          <t>VZ Expost OPPIK_final.docx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>OP PIK</t>
+          <t>OP Z</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01.026.01</t>
+          <t>03.045.01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OP PIK  •  Ex post evaluace OP PIK a replikace kontrafaktuální dopadové analýzy OP PI</t>
+          <t>OP Z  •  Evaluace výzvy 130 - genderové re-audity</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ex post evaluace OP PIK a replikace kontrafaktuální dopadové analýzy OP PI</t>
+          <t>Evaluace výzvy 130 - genderové re-audity</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vstupní zpráva</t>
+          <t>Zpracování případových studií a vyhodnocení projektů podpořených ve výzvě č. 130 OPZ na podporu implementace doporučení genderového auditu</t>
         </is>
       </c>
       <c r="F45" s="2">
-        <v>44929</v>
+        <v>44926</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4540,199 +4545,204 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Komplexní souhrnná evaluace dopadů Operačního programu Podnikání a inovace pro konkurenceschopnost 2014?2020 (dále též ?OP PIK?) a opětovné kontrafaktuální vyhodnocení dopadů již dříve zpracované evaluace dopadů Operačního programu Podnikání a inovace za období 2007?2013 (déle též ?OP PI?). Primárním účelem je zjištění dopadů podpory poskytované z Evropských strukturálních a investičních fondů na konkurenceschopnost podpořených podniků, a to jak v krátkém (OP PIK), tak ve střednědobém období (OP PI). Na základě vyhodnocení se taktéž očekávají doporučení pro optimalizaci nastavení jednotlivých intervencí ve vztahu k implementaci Operačního programu Technologie a aplikace pro konkurenceschopnost 2021?2027 (dále též ?OP TAK?).</t>
+          <t>Evaluace bude sloužit k vyhodnocení projektů z výzvy č. 130 na podporu implementace výsledků genderových auditů z hlediska přínosů pro cílové skupiny zaměstnavatelů a zaměstnanců, a posoudit vhodnost nastavení výzvy prostřednictvím vypracování 8 případových studií.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
-        <is>
-          <t>Obsahuje zejména metodický přístup k řešení evaluačních otázek, souhrn dosavadního zjištění a soubor z nich plynoucích hypotéz. Vstupní zpráva rovněž obsahuje závazný harmonogram plnění projektu, včetně stanovení termínů realizace terénních šetření a specifikace lhůt pro případnou součinnost ze strany zadavatele.</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Nerelevantní pro tuto etapu</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Dopad/výsledky</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>ex-post</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Strategická, Dopadová/Výsledková</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTkwODUxOTQwMztQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>VZ Expost OPPIK_final.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>OP Z</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>03.045.01</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>OP Z  •  Evaluace výzvy 130 - genderové re-audity</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Evaluace výzvy 130 - genderové re-audity</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Zpracování případových studií a vyhodnocení projektů podpořených ve výzvě č. 130 OPZ na podporu implementace doporučení genderového auditu</t>
-        </is>
-      </c>
-      <c r="F46" s="2">
-        <v>44926</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Evaluace bude sloužit k vyhodnocení projektů z výzvy č. 130 na podporu implementace výsledků genderových auditů z hlediska přínosů pro cílové skupiny zaměstnavatelů a zaměstnanců, a posoudit vhodnost nastavení výzvy prostřednictvím vypracování 8 případových studií.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">Cílem evaluačního výzkumu je v 8 případových studiích kriticky zhodnotit přínos osmi vybraných projektů s ohledem na potřeby aktérů a prosazování genderové rovnosti v praxi u různých typů zaměstnavatelů. Případové studie mají přinést detailní vhled do problematiky implementace genderových auditů u zaměstnavatelů v České republice, zachytit (dobrou) praxi ve způsobech prosazování genderové rovnosti na pracovišti a zmapovat všechny efekty, k nimž daná intervence směřuje. Zpracovatel  v druhém evaluačním úkolu poznatky získané v případových studiích kriticky posoudí, porovná a shrne. Pokud to data umožní navrhne rovněž zobecňující závěry, které bude možné využít jak pro efektivní nastavení navazujících výzev, tak i pro další evaluační aktivity v této oblasti. 
 V druhé polovině roku 2022 probíhá akceptace závěrečné evaluační zprávy. </t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>1)	Vyšší udržitelnost změn do budoucna byla zjištěna v organizacích, ve kterých se podařilo udržet na personálním oddělení pracovníka nebo pracovnici se znalostí a vhledem do témat rovných příležitostí než tam, kde taková kompetentní osoba odešla, nebo nebyla přítomna vůbec. 
 2)	Projekty, ve kterých po celou dobu realizace působil genderový odborník/odbornice, byly úspěšnější z hlediska přínosu pro zaměstnance /zaměstnankyně, dařilo se jim udržet nastavené aktivity a pracovat s nimi, a to i přes komplikovanou pandemickou situaci.
 3)	Mezi evaluovanými projekty byla zjištěna dobrá praxe sdílení zkušeností prostřednictvím workshopů, či výjezdních setkání (viz případová studie VI). V tomto případě byl oceňován zejména vhled do způsobu řešení genderových témat a sdílení inspirace v přístupu k potřebám v oblasti Age managementu a v přístupu k diverzitě.</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>Jiná</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>ex-post</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTc0MDE5MDQyNztQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>Záverečná evaluační zpráva_Technická příloha.pdf</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>OP Z</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>03.044.03</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>OP Z  •  Evaluace výsledků výzvy Podpora programu Housing First (Bydlení především)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Evaluace výsledků výzvy Podpora programu Housing First (Bydlení především)</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t xml:space="preserve">Případové studie projektů výzvy Podpora programu Housing First </t>
         </is>
       </c>
-      <c r="F47" s="2">
+      <c r="F46" s="2">
         <v>44925</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>ukončeno</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Vyhodnotit přínosy projektů z výzvy na podporu pilotního rozšíření konceptu Housing First / Bydlení především pro cílové skupiny.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">Cílem případových studií je zachytit zkušenosti realizátorů z pilotního využití přístupu Housing First k zabydlování osob bez domova a v bytové nouzi. Cílem je podpora šíření dobré praxe v oblasti sociálního bydlení. Zjištění z této studie mají sloužit zejména neziskovým organizacím či obcím, které se chtějí dozvědět více informací o realizaci projektu Housing First a případně zvažují vlastní aktivity v tomto směru. </t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t xml:space="preserve">Případová studie Bydlení především: Testování konceptu Housing First v Jihlavě se zaměřuje na zkušenosti z realizace projektu , konkrétně na důležité fáze projektu jako jsou zajištění bytů pro projekt, registrační týden (mapování osob v bytové nouzi) nebo výběr potřebných osob k zabydlení apod. Dále se studie zabývá postupy, které se v realizaci projektu osvědčily, ale i problémy, se kterými se museli zástupci projektu vypořádat. Cílem případové studie je sdílení zkušeností z realizace projektu všem, kteří se o problematiku sociálního bydlení zajímají, obzvláště obcím a neziskovým organizacím, které zvažují realizaci obdobného projektu. Případová studie vznikla na základě rozhovorů s klíčovými osobami, které se podílely na realizaci projektu nebo úzce spolupracovali s realizačním týmem.
 Případová studie Romodrom: Housing First v Moravskoslezském kraji se zaměřuje na zkušenosti realizátorů z pilotního využití přístupu Housing First k zabydlování osob bez domova a v bytové nouzi. Zjištění z této studie mají sloužit zejména neziskovým organizacím, které se chtějí dozvědět více informací o realizaci projektu Housing First a případně zvažují vlastní aktivity v tomto směru. Případová studie se zaměřuje na motivaci k realizaci projektu, sestavení realizačního týmu, zajištění bytů pro projekt, párování bytů s podpořenými osobami či rodinami a také na předcházení sousedským sporům a dluhům na nájmu, což jsou klíčové aspekty pro prodlužování nájemních smluv, a tudíž i pro udržení bydlení. 
 </t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Jiná</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>plnění cílů</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>mid-term</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Tematická</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTU0MTg2NzYzMTtQcmlsb2hhRE1TO0ZhbHNl</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>PS HF Jihlava.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>IROP</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>06.013.01</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>IROP  •  Shrnutí z evaluací IROP</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Shrnutí z evaluací IROP</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Shrnutí z evaluací IROP</t>
+        </is>
+      </c>
+      <c r="F47" s="2">
+        <v>44924</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Shrnutí z evaluací IROP realizovaných do roku 2022.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Shrnutí z evaluací IROP realizovaných do roku 2022.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Pouze shrnutí předchozího.</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>Ano</t>
@@ -4753,60 +4763,50 @@
           <t>Jiná</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>plnění cílů</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>mid-term</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Tematická</t>
+          <t>ex-post</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTU0MTg2NzYzMTtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTc3NTE0OTY2NjtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>PS HF Jihlava.pdf</t>
+          <t>Shrnutí z evaluací IROP.pdf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IROP</t>
+          <t>PRV</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>06.013.01</t>
+          <t>09.003.13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IROP  •  Shrnutí z evaluací IROP</t>
+          <t>PRV  •  Zpracování odpovědí na hodnotící otázky vztažené k prioritním oblastem PRV a technické pomoci PRV</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Shrnutí z evaluací IROP</t>
+          <t>Zpracování odpovědí na hodnotící otázky vztažené k prioritním oblastem PRV a technické pomoci PRV</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Shrnutí z evaluací IROP</t>
+          <t>Dvanáctá zpráva o hodnocení PRV 2014-2020 - září 2022</t>
         </is>
       </c>
       <c r="F48" s="2">
-        <v>44924</v>
+        <v>44909</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4815,17 +4815,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Shrnutí z evaluací IROP realizovaných do roku 2022.</t>
+          <t>Zpracování odpovědí na hodnotící otázky pro každou prioritní oblast  zahrnutou v PRV (vč. technické pomoci, Celostátní sítě pro venkov a oblasti, synergií a komplementarit ), vyhodnocení příspěvku PRV k plnění cílů SZP a Strategie EU 2020. Výstupy budou využity jako příprava pro další fáze průběžného hodnocení a ex post hodnocení, zároveň budou sloužit jako podklad pro MMR - NOK k vyhodnocení plnění cílů Dohody o partnerství.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Shrnutí z evaluací IROP realizovaných do roku 2022.</t>
+          <t>Hodnocení PRV na datech k 30.6.2022.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Pouze shrnutí předchozího.</t>
+          <t>viz hodnotící zpráva</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4845,53 +4845,58 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Jiná</t>
+          <t>Dopad/výsledky</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>ex-post</t>
+          <t>on-going</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Strategická, Tematická, Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTc3NTE0OTY2NjtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTc0NTI3OTA5NTtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Shrnutí z evaluací IROP.pdf</t>
+          <t>PHZ_2_2022_sloučený.pdf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PRV</t>
+          <t>OP VVV</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>09.003.13</t>
+          <t>02.011.06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PRV  •  Zpracování odpovědí na hodnotící otázky vztažené k prioritním oblastem PRV a technické pomoci PRV</t>
+          <t>OP VVV  •  Evaluace IPs PO3 OP VVV - II.: (APIV A, APIV B, KSH, MOV, PPUČ)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Zpracování odpovědí na hodnotící otázky vztažené k prioritním oblastem PRV a technické pomoci PRV</t>
+          <t>Evaluace IPs PO3 OP VVV - II.: (APIV A, APIV B, KSH, MOV, PPUČ)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dvanáctá zpráva o hodnocení PRV 2014-2020 - září 2022</t>
+          <t>Evaluace Akčních plánů inkluzivního vzdělávání (APIV): Závěrečná zpráva 2022</t>
         </is>
       </c>
       <c r="F49" s="2">
-        <v>44909</v>
+        <v>44895</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -4900,17 +4905,17 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Zpracování odpovědí na hodnotící otázky pro každou prioritní oblast  zahrnutou v PRV (vč. technické pomoci, Celostátní sítě pro venkov a oblasti, synergií a komplementarit ), vyhodnocení příspěvku PRV k plnění cílů SZP a Strategie EU 2020. Výstupy budou využity jako příprava pro další fáze průběžného hodnocení a ex post hodnocení, zároveň budou sloužit jako podklad pro MMR - NOK k vyhodnocení plnění cílů Dohody o partnerství.</t>
+          <t>Průběžné hodnocení projektů APIV A, APIV B, KSH, MOV, PPUČ</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Hodnocení PRV na datech k 30.6.2022.</t>
+          <t>Závěrečná zpráva projektů APIV A a B</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>viz hodnotící zpráva</t>
+          <t>Viz dokument</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4940,48 +4945,48 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Strategická, Tematická, Dopadová/Výsledková</t>
+          <t>Strategická, Operativní/procesní, Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTc0NTI3OTA5NTtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7NjA0NTg1MzQ4O1ByaWxvaGFETVM7RmFsc2U=</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>PHZ_2_2022_sloučený.pdf</t>
+          <t>APIV_final_report.pdf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>OP VVV</t>
+          <t>OP Z</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>02.011.06</t>
+          <t>03.049.01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OP VVV  •  Evaluace IPs PO3 OP VVV - II.: (APIV A, APIV B, KSH, MOV, PPUČ)</t>
+          <t>OP Z  •  Výsledková evaluace OPZ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Evaluace IPs PO3 OP VVV - II.: (APIV A, APIV B, KSH, MOV, PPUČ)</t>
+          <t>Výsledková evaluace OPZ</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Evaluace Akčních plánů inkluzivního vzdělávání (APIV): Závěrečná zpráva 2022</t>
+          <t>Výsledková evaluace OPZ - Hodnocení specifických cílů OPZ 2014-2022</t>
         </is>
       </c>
       <c r="F50" s="2">
-        <v>44895</v>
+        <v>44883</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4990,17 +4995,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Průběžné hodnocení projektů APIV A, APIV B, KSH, MOV, PPUČ</t>
+          <t>Předmětem je vyhodnocení plnění specifických cílů OPZ na základě dosud vyhlášených výzev a realizovaných projektů a jimi dosažených souhrnných hodnot výstupových a výsledkových indikátorů. Bude provedena syntéza výstupů ze samostatných především výsledkových evaluací jednotlivých IP/SC OPZ, příp. jiných relevantních hodnocení, které jsou realizovány v rámci jiných evaluací OPZ.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Závěrečná zpráva projektů APIV A a B</t>
+          <t xml:space="preserve">Předmětem je vyhodnocení plnění specifických cílů OPZ na základě dosud vyhlášených výzev a realizovaných projektů a jimi dosažených souhrnných hodnot výstupových a výsledkových indikátorů. Bude provedena syntéza výstupů ze samostatných především výsledkových evaluací jednotlivých IP/SC OPZ, příp. jiných relevantních hodnocení, které jsou realizovány v rámci jiných evaluací OPZ. 
+Jedná se o strategické vyhodnocení pokroku  v implementaci OPZ v závěrečné fázi jeho realizace a syntézu závěrů provedených evaluací a dosažených výstupů a výsledků dle čl. 114 Nařízení č. 1303/2013.  </t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Viz dokument</t>
+          <t xml:space="preserve">Z hlediska výstupových a především výsledkových indikátorů byly jejich předběžně stanovené cílové hodnoty ve většině případů již v této fázi administrace operačního programu naplněny. U další řady indikátorů lze vzhledem k aktuálním hodnotám a zahájeným projektům naplnění jejich cílových hodnot očekávat s ukončením všech realizovaných intervencí. V nižším počtu případů byly cílové hodnoty i několikanásobně překonány, u jiných naopak teprve ukončení klíčových běžících projektů ukáže, v jaké míře byly očekávané hodnoty realistické, což ukazuje na obtížnost předjímání průběhu administrace operačního programu.
+Ve všech jednotlivých investičních prioritách potažmo v rámci evaluační podpory administrace jednotlivých typů podpor operačního programu byly provedeny desítky evaluací a analýz, přičemž další šetření v současné době probíhají. Závěry z těchto evaluací z kvalitativního hlediska dokreslují dosažené výstupy a výsledky programu. </t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5023,55 +5030,60 @@
           <t>Dopad/výsledky</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>plnění cílů</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>on-going</t>
+          <t>ad-hoc</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Strategická, Operativní/procesní, Dopadová/Výsledková</t>
+          <t>Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7NjA0NTg1MzQ4O1ByaWxvaGFETVM7RmFsc2U=</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTY4NTA5NDc4MDtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>APIV_final_report.pdf</t>
+          <t>Výsledková evaluace OPZ.pdf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OP Z</t>
+          <t>OP PIK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>03.049.01</t>
+          <t>01.024.02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>OP Z  •  Výsledková evaluace OPZ</t>
+          <t>OP PIK  •  Předběžné posouzení finančních nástrojů OP TAK</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Výsledková evaluace OPZ</t>
+          <t>Předběžné posouzení finančních nástrojů OP TAK</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Výsledková evaluace OPZ - Hodnocení specifických cílů OPZ 2014-2022</t>
+          <t>Předběžné posouzení finančních nástrojů OP TAK: Závěrečná zpráva</t>
         </is>
       </c>
       <c r="F51" s="2">
-        <v>44883</v>
+        <v>44859</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -5080,112 +5092,15 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Předmětem je vyhodnocení plnění specifických cílů OPZ na základě dosud vyhlášených výzev a realizovaných projektů a jimi dosažených souhrnných hodnot výstupových a výsledkových indikátorů. Bude provedena syntéza výstupů ze samostatných především výsledkových evaluací jednotlivých IP/SC OPZ, příp. jiných relevantních hodnocení, které jsou realizovány v rámci jiných evaluací OPZ.</t>
+          <t>Předmětem plnění této evaluační zakázky je vypracování Předběžného posouzení finančních nástrojů Operačního programu Technologie a aplikace pro konkurenceschopnost 2021 - 2027 za předem stanovených podmínek. S tím souvisí i případné dodatečné práce při aktualizaci Vypracování Předběžného posouzení finančních nástrojů Operačního programu Technologie a aplikace pro konkurenceschopnost 2021 - 2027, o které může objednatel požádat do 20ti měsíců od akceptace Závěrečné zprávy a to v rozsahu max. 500 hodin opět za předem stanovených podmínek ve Smlouvě.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Předmětem je vyhodnocení plnění specifických cílů OPZ na základě dosud vyhlášených výzev a realizovaných projektů a jimi dosažených souhrnných hodnot výstupových a výsledkových indikátorů. Bude provedena syntéza výstupů ze samostatných především výsledkových evaluací jednotlivých IP/SC OPZ, příp. jiných relevantních hodnocení, které jsou realizovány v rámci jiných evaluací OPZ. 
-Jedná se o strategické vyhodnocení pokroku  v implementaci OPZ v závěrečné fázi jeho realizace a syntézu závěrů provedených evaluací a dosažených výstupů a výsledků dle čl. 114 Nařízení č. 1303/2013.  </t>
+          <t>Předmětem veřejné zakázky je zpracování Předběžného posouzení finančních nástrojů Operačního programu Technologie a Aplikace pro konkurenceschopnost v rozsahu předpokládaném legislativou. Finanční nařízení  definuje finanční nástroj v čl. 2 odst. 29) jako opatření finanční podpory Unie poskytovaná z rozpočtu na doplňkovém základě a zaměřená na plnění jednoho nebo více konkrétních politických cílů Unie. Tyto nástroje mohou mít formu kapitálových či kvazikapitálových investic, půjček nebo záruk anebo jiných nástrojů ke sdílení rizik. Tam, kde je to vhodné, mohou být spojeny s granty.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z hlediska výstupových a především výsledkových indikátorů byly jejich předběžně stanovené cílové hodnoty ve většině případů již v této fázi administrace operačního programu naplněny. U další řady indikátorů lze vzhledem k aktuálním hodnotám a zahájeným projektům naplnění jejich cílových hodnot očekávat s ukončením všech realizovaných intervencí. V nižším počtu případů byly cílové hodnoty i několikanásobně překonány, u jiných naopak teprve ukončení klíčových běžících projektů ukáže, v jaké míře byly očekávané hodnoty realistické, což ukazuje na obtížnost předjímání průběhu administrace operačního programu.
-Ve všech jednotlivých investičních prioritách potažmo v rámci evaluační podpory administrace jednotlivých typů podpor operačního programu byly provedeny desítky evaluací a analýz, přičemž další šetření v současné době probíhají. Závěry z těchto evaluací z kvalitativního hlediska dokreslují dosažené výstupy a výsledky programu. </t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Dopad/výsledky</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>plnění cílů</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>ad-hoc</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>Dopadová/Výsledková</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTY4NTA5NDc4MDtQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>Výsledková evaluace OPZ.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>OP PIK</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>01.024.02</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>OP PIK  •  Předběžné posouzení finančních nástrojů OP TAK</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Předběžné posouzení finančních nástrojů OP TAK</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Předběžné posouzení finančních nástrojů OP TAK: Závěrečná zpráva</t>
-        </is>
-      </c>
-      <c r="F52" s="2">
-        <v>44859</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Předmětem plnění této evaluační zakázky je vypracování Předběžného posouzení finančních nástrojů Operačního programu Technologie a aplikace pro konkurenceschopnost 2021 - 2027 za předem stanovených podmínek. S tím souvisí i případné dodatečné práce při aktualizaci Vypracování Předběžného posouzení finančních nástrojů Operačního programu Technologie a aplikace pro konkurenceschopnost 2021 - 2027, o které může objednatel požádat do 20ti měsíců od akceptace Závěrečné zprávy a to v rozsahu max. 500 hodin opět za předem stanovených podmínek ve Smlouvě.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Předmětem veřejné zakázky je zpracování Předběžného posouzení finančních nástrojů Operačního programu Technologie a Aplikace pro konkurenceschopnost v rozsahu předpokládaném legislativou. Finanční nařízení  definuje finanční nástroj v čl. 2 odst. 29) jako opatření finanční podpory Unie poskytovaná z rozpočtu na doplňkovém základě a zaměřená na plnění jednoho nebo více konkrétních politických cílů Unie. Tyto nástroje mohou mít formu kapitálových či kvazikapitálových investic, půjček nebo záruk anebo jiných nástrojů ke sdílení rizik. Tam, kde je to vhodné, mohou být spojeny s granty.</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">Cílem navržených FN je podpora specifických aktivit v rámci jednotlivých specifických cílů: 
 - V rámci SC 1.2 se jedná o Digitální podnik a Technologie 4.0 s FN ve formě 80 % záruky za komerční úvěr nebo zvýhodněný úvěr s dotací 30 % a technickou asistencí, případně doplněný o záruční/úvěrový finanční nástroj kombinovaný s dotací pro aktivitu Datová centra
@@ -5197,93 +5112,93 @@
 SC 5.1 byl vyhodnocen jako nevhodný pro financování finančními nástroji. </t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>Jiná</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>ex-ante</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>Strategická</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTY5MzQwODk4MztQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>Předběžné posouzení finančních nástrojů OP TAK_Závěrečná zpráva.docx</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>OP ZP</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>05.007.01</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>OP ZP  •  Zhodnocení dosavadního pokroku při dosahování cílů OPŽP 2014-2020 II</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Zhodnocení dosavadního pokroku při dosahování cílů OPŽP 2014-2020 II</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Zhodnocení dosavadního pokroku při dosahování cílů OPŽP 2014-2020 II</t>
         </is>
       </c>
-      <c r="F53" s="2">
+      <c r="F52" s="2">
         <v>44852</v>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>ukončeno</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>Cílem evaluace je kvantifikovat přínosy / efekty intervencí zaměřených na zlepšování určitých oblastí nebo zmírňování určitých negativních dopadů a 
 evaluovat efekty, které se projevily v rámci sledovaného programového období.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">Cílem projektu je hodnocení naplňování cílů OPŽP v programovém období 2014-2020 s důrazem na dosažené výsledky. </t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t xml:space="preserve">? daří se úspěšně čerpat alokaci zejména u prioritních os 1 a 3, největší komplikace měla s čerpáním v čase hodnocení prioritní osa 5
 ? z hlediska množství proinvestovaných prostředků se daří naplnit stanovené závazky
@@ -5293,6 +5208,101 @@
 </t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Dopad/výsledky</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>plnění cílů</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>on-going</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Dopadová/Výsledková</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTA5Mzc4OTk5OTtQcmlsb2hhRE1TO0ZhbHNl</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>221011_OPŽP_II_Evaluacni_zprava_cista_verze.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PRV</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>09.004.06</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>PRV  •  Předběžné hodnocení Strategického plánu SZP pro období 2021-2027</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Předběžné hodnocení Strategického plánu SZP pro období 2021-2027</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2. aktualizace ex-ante hodnocení SP SZP 2023-2027</t>
+        </is>
+      </c>
+      <c r="F53" s="2">
+        <v>44834</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Hodnocení ex-ante se provádí na základě evropského nařízení za účelem zlepšit kvalitu koncepce SP SZP (obsahuje SWOT analýzu, vyhodnocení potřeb dle specifických cílů, intervenční strategie, finančních rozpočtů, řídící struktury, popis prvků k modernizaci a zjednodušení SZP)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Doplnění hodnocení po připomínkách EK.</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>viz hodnotící zpráva</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>Ano</t>
@@ -5313,60 +5323,45 @@
           <t>Dopad/výsledky</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>plnění cílů</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>on-going</t>
+          <t>ex-ante</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Dopadová/Výsledková</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTA5Mzc4OTk5OTtQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>221011_OPŽP_II_Evaluacni_zprava_cista_verze.pdf</t>
+          <t>Strategická, Tematická, Dopadová/Výsledková</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PRV</t>
+          <t>OP VVV</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>09.004.06</t>
+          <t>02.002.13</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PRV  •  Předběžné hodnocení Strategického plánu SZP pro období 2021-2027</t>
+          <t>OP VVV  •  Průběžná evaluace implementace OP VVV</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Předběžné hodnocení Strategického plánu SZP pro období 2021-2027</t>
+          <t>Průběžná evaluace implementace OP VVV</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2. aktualizace ex-ante hodnocení SP SZP 2023-2027</t>
+          <t>Průběžná evaluace implementace OP VVV - Průběžná zpráva k 15. 9. 2022</t>
         </is>
       </c>
       <c r="F54" s="2">
-        <v>44834</v>
+        <v>44819</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -5375,17 +5370,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Hodnocení ex-ante se provádí na základě evropského nařízení za účelem zlepšit kvalitu koncepce SP SZP (obsahuje SWOT analýzu, vyhodnocení potřeb dle specifických cílů, intervenční strategie, finančních rozpočtů, řídící struktury, popis prvků k modernizaci a zjednodušení SZP)</t>
+          <t>Průběžné hodnocení věcného a finančního pokroku OP VVV + tematická hodnocení (hodnocení prvních výzev, hodnocení S/K vazeb, hodnocení TP, hodnocení multifondovosti, hodnocení horizontálních principů, podklady pro MMR-NOK v roce 2017 a 2019)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Doplnění hodnocení po připomínkách EK.</t>
+          <t>Vyhodnocení věcného a finančního pokroku OP VVV</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>viz hodnotící zpráva</t>
+          <t>Závěry uvedeny v dokumentu.</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5405,17 +5400,32 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Dopad/výsledky</t>
+          <t>Jiná</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>plnění cílů</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>ex-ante</t>
+          <t>on-going</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Strategická, Tematická, Dopadová/Výsledková</t>
+          <t>Operativní/procesní</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODE0MTY1MTc7UHJpbG9oYURNUztGYWxzZQ==</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>MSMT_Prubezna evaluace_Prubezna zprava 13_Man.shrnuti.pdf</t>
         </is>
       </c>
     </row>
@@ -5427,26 +5437,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>02.002.13</t>
+          <t>02.006.04</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OP VVV  •  Průběžná evaluace implementace OP VVV</t>
+          <t>OP VVV  •  Evaluace IPs PO 3 OP VVV - III.: Evaluace systémového projektu "SYPO"</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Průběžná evaluace implementace OP VVV</t>
+          <t>Evaluace IPs PO 3 OP VVV - III.: Evaluace systémového projektu "SYPO"</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Průběžná evaluace implementace OP VVV - Průběžná zpráva k 15. 9. 2022</t>
+          <t>Evaluace IPs PO 3 OP VVV - III.: Evaluace systémového projektu "SYPO": 2. Průběžná zpráva</t>
         </is>
       </c>
       <c r="F55" s="2">
-        <v>44819</v>
+        <v>44816</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -5455,17 +5465,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Průběžné hodnocení věcného a finančního pokroku OP VVV + tematická hodnocení (hodnocení prvních výzev, hodnocení S/K vazeb, hodnocení TP, hodnocení multifondovosti, hodnocení horizontálních principů, podklady pro MMR-NOK v roce 2017 a 2019)</t>
+          <t>Hodnocení účelnosti a účinnosti intervencí při dosahování cílů individuálních projektů systémových (IPs) a individuálních projektů s koncepčním charakterem  (IPk) PO3</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Vyhodnocení věcného a finančního pokroku OP VVV</t>
+          <t>Vyhodnocení všech evaluačních otázek pro 2. průběžnou zprávu</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Závěry uvedeny v dokumentu.</t>
+          <t>viz evaluační zpráva</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5485,12 +5495,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Jiná</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>plnění cílů</t>
+          <t>Dopad/výsledky</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5500,44 +5505,44 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Operativní/procesní</t>
+          <t>Operativní/procesní, Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODE0MTY1MTc7UHJpbG9oYURNUztGYWxzZQ==</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTU4MDU4NTU1MTtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>MSMT_Prubezna evaluace_Prubezna zprava 13_Man.shrnuti.pdf</t>
+          <t>SYPO_2. Prubezna zprava_final.pdf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>OP VVV</t>
+          <t>PRV</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>02.006.04</t>
+          <t>09.005.04</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OP VVV  •  Evaluace IPs PO 3 OP VVV - III.: Evaluace systémového projektu "SYPO"</t>
+          <t>PRV  •  Analýza SEA Strategického plánu SZP pro období 2021-2027</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Evaluace IPs PO 3 OP VVV - III.: Evaluace systémového projektu "SYPO"</t>
+          <t>Analýza SEA Strategického plánu SZP pro období 2021-2027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Evaluace IPs PO 3 OP VVV - III.: Evaluace systémového projektu "SYPO": 2. Průběžná zpráva</t>
+          <t>d) Spolupráce při veřejném projednání koncepce Strategického plánu SZP (včetně zápisu z jednání a vypořádávání podaných připomínek)</t>
         </is>
       </c>
       <c r="F56" s="2">
@@ -5549,111 +5554,111 @@
         </is>
       </c>
       <c r="H56" t="inlineStr">
-        <is>
-          <t>Hodnocení účelnosti a účinnosti intervencí při dosahování cílů individuálních projektů systémových (IPs) a individuálních projektů s koncepčním charakterem  (IPk) PO3</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Vyhodnocení všech evaluačních otázek pro 2. průběžnou zprávu</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>viz evaluační zpráva</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Dopad/výsledky</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>on-going</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>Operativní/procesní, Dopadová/Výsledková</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTU4MDU4NTU1MTtQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>SYPO_2. Prubezna zprava_final.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>PRV</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>09.005.04</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>PRV  •  Analýza SEA Strategického plánu SZP pro období 2021-2027</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Analýza SEA Strategického plánu SZP pro období 2021-2027</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>d) Spolupráce při veřejném projednání koncepce Strategického plánu SZP (včetně zápisu z jednání a vypořádávání podaných připomínek)</t>
-        </is>
-      </c>
-      <c r="F57" s="2">
-        <v>44816</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
         <is>
           <t xml:space="preserve">Zajištění celého procesu posuzování vlivu Strategického plánu SZP 
 na období 2021-2027 na životní prostředí podle zákona č. 100/2001 Sb., o posuzování vlivů na životní prostředí a o změně některých souvisejících zákonů (zákon o posuzování vlivů na životní prostředí), ve znění pozdějších předpisů.
 </t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">a. Veřejné projednání SEA, zahrnující zpracování informace o veřejném projednání pro účely zveřejnění (na úřední desce MZe, na internetu a v tisku) a informování příslušného úřadu o místě a čase konání veřejného projednávání, prezentace výstupů SEA na veřejném projednání, vytvoření zápisu a spolupráce při vypořádání a zapracování podaných připomínek.
 b. V této souvislosti navrhne zpracovatel způsob, který je podle jeho názoru a zkušeností nejvhodnější pro zapojení veřejnosti do procesu posuzování vlivů na životní prostředí a veřejné zdraví. Zpracovatel bude veřejné projednání řídit (moderovat) a pořídí z veřejného projednání zápis, který projedná s objednatelem. </t>
         </is>
       </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>viz zápis z VP</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Dopad/výsledky</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>ad-hoc</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Strategická, Tematická, Dopadová/Výsledková</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTY4MzI5NDE4ODtQcmlsb2hhRE1TO0ZhbHNl</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>SEA SP SZP_výstup k dílčímu plnění D_Zápis z VP 25.8.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>OP Z</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>03.003.01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>OP Z  •  Zpětná vazba klientů OPZ</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Zpětná vazba klientů OPZ</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Zpětná vazba klientů OPZ_Dotazníková šetření</t>
+        </is>
+      </c>
+      <c r="F57" s="2">
+        <v>44805</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Opakované vyhodnocení nastavení a fungování procesů administrace přípravy, výběru a realizace projektů OPZ na základě získávání zpětné vazby od klientů OPZ, vč. měření indikátoru míry spokojenosti klientů celkově a s jednotlivými procesními oblastmi.  Analýza výstupů garanty procesů na ŘO OPZ a zahrnutí jejich pohledu.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Opakované vyhodnocení nastavení a fungování procesů administrace přípravy, výběru a realizace projektů OPZ na základě získávání zpětné vazby od klientů OPZ, vč. měření indikátoru míry spokojenosti klientů celkově a s jednotlivými procesními oblastmi.  Analýza výstupů garanty procesů na ŘO OPZ a zahrnutí jejich pohledu.</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>viz zápis z VP</t>
+          <t>Sběr dat, vyhodnocení a interpretace prvního šetření proběhlo v první polovině roku 2017. Záverečná zpráva byla rozeslána členům PSE OPZ 23. 5. 2017. Sběr dat, vyhodnocení a interpretace druhého šetření proběhlo v první polovině roku 2018. Závěrečná zpráva byla rozeslána členům PSE OPZ 22. 5. 2018. Sběr dat, vyhodnocení a interpretace třetího šetření proběhlo v první polovině roku 2019. Závěrečná zpráva byla rozeslána členům PSE OPZ 12. 6. 2019. Vzhledem ke konzistentním výsledkům šetření za předchozí 3 roky a absenci významných změn v prostředí administrace projektů v OPZ, které by mohly vyvolat změny postojů respondentů, nebyla šetření za další roky realizována.</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5673,58 +5678,58 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Dopad/výsledky</t>
+          <t>Jiná</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>ad-hoc</t>
+          <t>on-going</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Strategická, Tematická, Dopadová/Výsledková</t>
+          <t>Operativní/procesní</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTY4MzI5NDE4ODtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7NTQyNjAyNTI7UHJpbG9oYURNUztGYWxzZQ==</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>SEA SP SZP_výstup k dílčímu plnění D_Zápis z VP 25.8.pdf</t>
+          <t>Zpráva z šetření zpětné vazby 2016.zip</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>OP Z</t>
+          <t>OP VVV</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>03.003.01</t>
+          <t>02.016.09</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OP Z  •  Zpětná vazba klientů OPZ</t>
+          <t>OP VVV  •  Výsledková evaluace OP VVV</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Zpětná vazba klientů OPZ</t>
+          <t>Výsledková evaluace OP VVV</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Zpětná vazba klientů OPZ_Dotazníková šetření</t>
+          <t>Výsledková evaluace OP VVV: Vyhodnocení postojů k inkluzivnímu vzdělávání</t>
         </is>
       </c>
       <c r="F58" s="2">
-        <v>44805</v>
+        <v>44804</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -5733,100 +5738,10 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Opakované vyhodnocení nastavení a fungování procesů administrace přípravy, výběru a realizace projektů OPZ na základě získávání zpětné vazby od klientů OPZ, vč. měření indikátoru míry spokojenosti klientů celkově a s jednotlivými procesními oblastmi.  Analýza výstupů garanty procesů na ŘO OPZ a zahrnutí jejich pohledu.</t>
+          <t>Cílem evaluace je  zhodnocení toho, jak podpora z fondů ESI přispěla k dosahování cílů jednotlivých priorit a specifických cílů OP VVV.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
-        <is>
-          <t>Opakované vyhodnocení nastavení a fungování procesů administrace přípravy, výběru a realizace projektů OPZ na základě získávání zpětné vazby od klientů OPZ, vč. měření indikátoru míry spokojenosti klientů celkově a s jednotlivými procesními oblastmi.  Analýza výstupů garanty procesů na ŘO OPZ a zahrnutí jejich pohledu.</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Sběr dat, vyhodnocení a interpretace prvního šetření proběhlo v první polovině roku 2017. Záverečná zpráva byla rozeslána členům PSE OPZ 23. 5. 2017. Sběr dat, vyhodnocení a interpretace druhého šetření proběhlo v první polovině roku 2018. Závěrečná zpráva byla rozeslána členům PSE OPZ 22. 5. 2018. Sběr dat, vyhodnocení a interpretace třetího šetření proběhlo v první polovině roku 2019. Závěrečná zpráva byla rozeslána členům PSE OPZ 12. 6. 2019. Vzhledem ke konzistentním výsledkům šetření za předchozí 3 roky a absenci významných změn v prostředí administrace projektů v OPZ, které by mohly vyvolat změny postojů respondentů, nebyla šetření za další roky realizována.</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Jiná</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>on-going</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>Operativní/procesní</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7NTQyNjAyNTI7UHJpbG9oYURNUztGYWxzZQ==</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>Zpráva z šetření zpětné vazby 2016.zip</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>OP VVV</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>02.016.09</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>OP VVV  •  Výsledková evaluace OP VVV</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Výsledková evaluace OP VVV</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Výsledková evaluace OP VVV: Vyhodnocení postojů k inkluzivnímu vzdělávání</t>
-        </is>
-      </c>
-      <c r="F59" s="2">
-        <v>44804</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Cílem evaluace je  zhodnocení toho, jak podpora z fondů ESI přispěla k dosahování cílů jednotlivých priorit a specifických cílů OP VVV.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
         <is>
           <t>Šetření k postojům veřejnosti k inkluzivnímu vzdělávání 
 Obecná populace 18+; Rodiče dětí v předškolním věku, žáků na
@@ -5839,7 +5754,7 @@
 Obecná populace 18+, 1028 respondentů; Rodiče, 849 respondentů</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>V
 rámci dosažení validnějších výsledků byly vytvořeny dva reprezentativní vzorky Prvním z nich je obecná populace 18
@@ -5869,77 +5784,77 @@
 mají již v této době dost práce zvládat ?normální třídu? natož třídu s dětmi se speciálními vzdělávacím</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>Jiná</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>on-going</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTcwMTM5NTExOTtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>MŠMT_OPVVV_Postoje k inkluzi (003).pdf</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>OP Z</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>03.027.03</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>OP Z  •  Hodnocení výsledků Strategie komunitně vedeného místního rozvoje - CLLD (I.)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Hodnocení výsledků Strategie komunitně vedeného místního rozvoje - CLLD (I.)</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Vyhodnocení přínosu spolupráce aktérů místních akčních skupin</t>
         </is>
       </c>
-      <c r="F60" s="2">
+      <c r="F59" s="2">
         <v>44804</v>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>ukončeno</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t xml:space="preserve">PO 2 - IP 2.3 - SC1:  Strategie komunitně vedeného místního rozvoje
 Výstupy požadované dle EP DoP. Evaluace využití integrovaných nástrojů a strategií: hodnocení procesů, obsahová analýza výzev, sledování systému NSK a RSK, dopady na cílové skupiny a relevance.
@@ -5952,19 +5867,114 @@
 </t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>V roce 2021 byla připravována další etapa evaluace - externí zakázka Vyhodnocení přínosu spolupráce aktérů místních akčních skupin, realizace zakázky proběhla mezi lednem a srpnem roku 2022.
 Předmětem plnění je vyhodnocení přínosu spolupráce aktérů místních akčních skupin (MAS) pro rozvoj území v rámci témat programového rámce Operačního programu Zaměstnanost (OPZ). Přínos bude zjišťován v rámci fokusních skupin se třemi skupinami aktérů komunitně vedeného místního rozvoje (CLLD) ? manažery MAS; starosty obcí či jinými relevantními zástupci obcí; a zástupci nestátních neziskových organizací a podnikatelského sektoru. Vedle toho je cílem také vypracování případových studií, jejichž záměrem je zachytit dobrou praxi fungování spolupráce místních aktérů na území MAS v rámci témat programového rámce OPZ.</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Místní akční skupiny byly všemi třemi skupinami aktérů považovány za užitečný nástroj, a to nejen v programovém rámci OPZ, ale i v dalších oblastech, kdy přispívají významnou měrou k setkávání všech relevantních aktérů v území.
 Z výpovědí respondentů vyplynulo, že projekty a aktivity MAS jsou vhodné pro podporu rozvoje sociální práce a také dalších forem podpory a pomoci ze strany komunity pro osoby ohrožené sociálním vyloučením (komunitní práce) v oblastech, kam sociální pracovníci ORP a sociálních služeb nemají takový dosah.
 Účastníci FS oceňovali možnost čerpat koordinovaně a integrovaně prostředky z IROP a z OPZ a také v té souvislosti nižší administrativní zátěž. Dalším významným přínosem MAS byla podle účastníků FS koordinace a lepší efektivita realizovaných projektů, kdy byla možnost spolupracovat s jinými organizacemi na stejných problémech v území, i když se předtím jednalo o konkurenty v soutěži v programových výzvách.</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Dopad/výsledky</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>plnění cílů</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>ex-post</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Operativní/procesní, Dopadová/Výsledková</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTM5ODM4MzM3MTtQcmlsb2hhRE1TO0ZhbHNl</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>MAS_Šumperský venkov_studie_final.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PRV</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>09.004.05</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PRV  •  Předběžné hodnocení Strategického plánu SZP pro období 2021-2027</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Předběžné hodnocení Strategického plánu SZP pro období 2021-2027</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1. aktualizace ex-ante hodnocení SP SZP 2023-2027</t>
+        </is>
+      </c>
+      <c r="F60" s="2">
+        <v>44799</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Hodnocení ex-ante se provádí na základě evropského nařízení za účelem zlepšit kvalitu koncepce SP SZP (obsahuje SWOT analýzu, vyhodnocení potřeb dle specifických cílů, intervenční strategie, finančních rozpočtů, řídící struktury, popis prvků k modernizaci a zjednodušení SZP)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Doplnění hodnocení po připomínkách z vnitřního připomínkového řízení (VPŘ) a meziresortu (MPŘ). </t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>viz Hodnotící zpráva</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>Ano</t>
@@ -5985,60 +5995,55 @@
           <t>Dopad/výsledky</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>plnění cílů</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>ex-post</t>
+          <t>ex-ante</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Operativní/procesní, Dopadová/Výsledková</t>
+          <t>Strategická, Tematická, Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTM5ODM4MzM3MTtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTY4MzEyMTAxNTtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>MAS_Šumperský venkov_studie_final.pdf</t>
+          <t>SZP_3 b) faze_zaverecna zprava_aktualizace 202208_v2.pdf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PRV</t>
+          <t>OP Z</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>09.004.05</t>
+          <t>03.015.04</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PRV  •  Předběžné hodnocení Strategického plánu SZP pro období 2021-2027</t>
+          <t>OP Z  •  Vyhodnocení výsledků podpory sociálních inovací v PO 3 OPZ</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Předběžné hodnocení Strategického plánu SZP pro období 2021-2027</t>
+          <t>Vyhodnocení výsledků podpory sociálních inovací v PO 3 OPZ</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1. aktualizace ex-ante hodnocení SP SZP 2023-2027</t>
+          <t xml:space="preserve">Analýzy nákladů a přínosů u vybraných sociálně inovačních projektů </t>
         </is>
       </c>
       <c r="F61" s="2">
-        <v>44799</v>
+        <v>44795</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -6047,17 +6052,18 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Hodnocení ex-ante se provádí na základě evropského nařízení za účelem zlepšit kvalitu koncepce SP SZP (obsahuje SWOT analýzu, vyhodnocení potřeb dle specifických cílů, intervenční strategie, finančních rozpočtů, řídící struktury, popis prvků k modernizaci a zjednodušení SZP)</t>
+          <t xml:space="preserve">Vyhodnocení příspěvku inovačních výzev k plnění SC PO 3  "Zvýšit kvalitu a kvantitu využívání sociálních inovací a mezinárodní spolupráce v tematických oblastech OPZ", včetně analýzy předpokladů a rizik dosažení cílů podpory. V rámci evaluace budou vyhodnoceny výzvy na podporu sociálních inovací a inovačního prostředí č. 018, 024 a 124.    </t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Doplnění hodnocení po připomínkách z vnitřního připomínkového řízení (VPŘ) a meziresortu (MPŘ). </t>
+          <t xml:space="preserve">Realizace Analýzy nákladů a přínosů u vybraných sociálně inovačních projektů, podpořených v rámci Operačního programu Zaměstnanost. Zakázka je dílčí součástí celkového Vyhodnocení výsledků podpory sociálních inovací v PO 3 OPZ. Jedním z cílů zakázky stanovených zadavatelem je zodpovědět, zda je u vybraného projektu při současné podobě nastavení inovačních výzev v rámci Operačního programu Zaměstnanost a se současnými dostupnými daty reálně možné Analýzu nákladů a přínosů realizovat, případně jaký typ dat je pro naplnění stanovených výzkumných cílů potřeba. V rámci zakázky by mělo dojít nejen k tomuto zhodnocení proveditelnosti a využitelnosti Analýzy nákladů a přínosů u vybraného projektu, ale také k identifikaci problémů a rizik při realizaci Analýzy nákladů a přínosů, spolu s definováním případných doporučení pro minimalizaci těchto rizik.
+Pokud se Analýza nákladů a přínosů ukáže u vybraného projektu jako proveditelná, bude dalším cílem zakázky zjistit, jaké efekty přináší daný projekt. V rámci zakázky by u daného projektu mělo dojít k změření ekonomického dopadu intervence ke sledování a vyčíslení finančních nákladů a výnosů spjatých s realizací projektu spolu se zhodnocením skutečných efektů projektu/inovace pro celou společnost (přímých i nepřímých). </t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>viz Hodnotící zpráva</t>
+          <t>V rámci VZMR došlo k zodpovězení výzkumné otázky, zda je u vybraných projektů reálně možné Analýzu nákladů a přínosů realizovat. V rámci zakázky došlo nejen k zhodnocení proveditelnosti a využitelnosti CBA, ale také k identifikaci problémů a rizik při realizaci, spolu s definováním doporučení pro jejich minimalizaci. U projektu Cochemský model výsledky analýzy ukázaly, že komplexní CBA není možné realizovat, jelikož data pro klíčové dopady intervence nebyla sbírána. Ideální evaluace by se opírala o dlouhodobý výzkum dospívání dětí, jenž by umožnil sledovat cílovou skupinu v dlouhém časovém období. U projektu Společně na Svobodu výsledky první fáze analýzy ukázaly, že komplexní CBA není možné realizovat, přestože mnohé aspekty komplexní CBA byly splněny. Slabinu představuje design experimentu kvůli nenáhodnému rozdělení cílové skupiny a malému vzorku. Dalším cílem zakázky bylo zjistit, jaké efekty přináší daný projekt, v ideálním případě skrze změření ekonomického dopadu intervence ke sledování a vyčíslení finančních nákladů a výnosů spjatých s realizací projektu spolu se zhodnocením skutečných efektů inovace pro celou společnost (přímých i nepřímých). V případě projektu Cochem bylo provedeno několik expertních odhadů, které se zaměřily na vybrané dopady: úspory časových kapacit sociálních pracovníků a úspory na straně soudu. Jedná se však o velmi dílčí odhady, na základě kterých nelze hodnotit celkové přínosy dané intervence, ani je nelze spolehlivě využít pro odhad dopadů při škálování. U projektu SnS byly zpřesněny výpočty nákladovosti trestné činnosti a recidivy, zejména zahrnutím dalších položek jako nehmotné škody. Konkrétně byly vyčísleny dvě stínové ceny, celkové společenské náklady trestného činu, o kterém nejsou dostupné žádné další informace, a trestného činu, po kterém následuje nepodmínečné odsouzení k VTOS. K finálnímu výpočtu a porovnání přínosů a nákladů v analýze nedošlo z důvodu nespolehlivosti naměřeného rozdílu v recidivě mezi KS a IS.</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6077,27 +6083,22 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Dopad/výsledky</t>
+          <t>Jiná</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>ex-ante</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Strategická, Tematická, Dopadová/Výsledková</t>
+          <t>ex-post</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTY4MzEyMTAxNTtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTM4MjkxMzQ5MjtQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>SZP_3 b) faze_zaverecna zprava_aktualizace 202208_v2.pdf</t>
+          <t>Smlouva_Cochemský model - RS.pdf</t>
         </is>
       </c>
     </row>
@@ -6109,26 +6110,26 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>03.015.04</t>
+          <t>03.048.01</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OP Z  •  Vyhodnocení výsledků podpory sociálních inovací v PO 3 OPZ</t>
+          <t>OP Z  •  Evaluace výzev 80 a 118 OPZ pro územní samosprávné celky</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Vyhodnocení výsledků podpory sociálních inovací v PO 3 OPZ</t>
+          <t>Evaluace výzev 80 a 118 OPZ pro územní samosprávné celky</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Analýzy nákladů a přínosů u vybraných sociálně inovačních projektů </t>
+          <t>Přínos vzdělávacích aktivit pro cílové skupiny</t>
         </is>
       </c>
       <c r="F62" s="2">
-        <v>44795</v>
+        <v>44773</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -6137,102 +6138,16 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vyhodnocení příspěvku inovačních výzev k plnění SC PO 3  "Zvýšit kvalitu a kvantitu využívání sociálních inovací a mezinárodní spolupráce v tematických oblastech OPZ", včetně analýzy předpokladů a rizik dosažení cílů podpory. V rámci evaluace budou vyhodnoceny výzvy na podporu sociálních inovací a inovačního prostředí č. 018, 024 a 124.    </t>
+          <t xml:space="preserve">Zhodnocení přínosů výzev 80 a 118 OPZ zaměřených na podporu řízení kvality a procesního řízení v organizaci, tvorbu strategických dokumentů, nástroje komunikace s veřejností a realizaci specifických vzdělávacích programů přispívajících ke zkvalitnění rozvoje lidských zdrojů ve veřejné správě. </t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Realizace Analýzy nákladů a přínosů u vybraných sociálně inovačních projektů, podpořených v rámci Operačního programu Zaměstnanost. Zakázka je dílčí součástí celkového Vyhodnocení výsledků podpory sociálních inovací v PO 3 OPZ. Jedním z cílů zakázky stanovených zadavatelem je zodpovědět, zda je u vybraného projektu při současné podobě nastavení inovačních výzev v rámci Operačního programu Zaměstnanost a se současnými dostupnými daty reálně možné Analýzu nákladů a přínosů realizovat, případně jaký typ dat je pro naplnění stanovených výzkumných cílů potřeba. V rámci zakázky by mělo dojít nejen k tomuto zhodnocení proveditelnosti a využitelnosti Analýzy nákladů a přínosů u vybraného projektu, ale také k identifikaci problémů a rizik při realizaci Analýzy nákladů a přínosů, spolu s definováním případných doporučení pro minimalizaci těchto rizik.
-Pokud se Analýza nákladů a přínosů ukáže u vybraného projektu jako proveditelná, bude dalším cílem zakázky zjistit, jaké efekty přináší daný projekt. V rámci zakázky by u daného projektu mělo dojít k změření ekonomického dopadu intervence ke sledování a vyčíslení finančních nákladů a výnosů spjatých s realizací projektu spolu se zhodnocením skutečných efektů projektu/inovace pro celou společnost (přímých i nepřímých). </t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>V rámci VZMR došlo k zodpovězení výzkumné otázky, zda je u vybraných projektů reálně možné Analýzu nákladů a přínosů realizovat. V rámci zakázky došlo nejen k zhodnocení proveditelnosti a využitelnosti CBA, ale také k identifikaci problémů a rizik při realizaci, spolu s definováním doporučení pro jejich minimalizaci. U projektu Cochemský model výsledky analýzy ukázaly, že komplexní CBA není možné realizovat, jelikož data pro klíčové dopady intervence nebyla sbírána. Ideální evaluace by se opírala o dlouhodobý výzkum dospívání dětí, jenž by umožnil sledovat cílovou skupinu v dlouhém časovém období. U projektu Společně na Svobodu výsledky první fáze analýzy ukázaly, že komplexní CBA není možné realizovat, přestože mnohé aspekty komplexní CBA byly splněny. Slabinu představuje design experimentu kvůli nenáhodnému rozdělení cílové skupiny a malému vzorku. Dalším cílem zakázky bylo zjistit, jaké efekty přináší daný projekt, v ideálním případě skrze změření ekonomického dopadu intervence ke sledování a vyčíslení finančních nákladů a výnosů spjatých s realizací projektu spolu se zhodnocením skutečných efektů inovace pro celou společnost (přímých i nepřímých). V případě projektu Cochem bylo provedeno několik expertních odhadů, které se zaměřily na vybrané dopady: úspory časových kapacit sociálních pracovníků a úspory na straně soudu. Jedná se však o velmi dílčí odhady, na základě kterých nelze hodnotit celkové přínosy dané intervence, ani je nelze spolehlivě využít pro odhad dopadů při škálování. U projektu SnS byly zpřesněny výpočty nákladovosti trestné činnosti a recidivy, zejména zahrnutím dalších položek jako nehmotné škody. Konkrétně byly vyčísleny dvě stínové ceny, celkové společenské náklady trestného činu, o kterém nejsou dostupné žádné další informace, a trestného činu, po kterém následuje nepodmínečné odsouzení k VTOS. K finálnímu výpočtu a porovnání přínosů a nákladů v analýze nedošlo z důvodu nespolehlivosti naměřeného rozdílu v recidivě mezi KS a IS.</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Jiná</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>ex-post</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTM4MjkxMzQ5MjtQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>Smlouva_Cochemský model - RS.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>OP Z</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>03.048.01</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>OP Z  •  Evaluace výzev 80 a 118 OPZ pro územní samosprávné celky</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Evaluace výzev 80 a 118 OPZ pro územní samosprávné celky</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Přínos vzdělávacích aktivit pro cílové skupiny</t>
-        </is>
-      </c>
-      <c r="F63" s="2">
-        <v>44773</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Zhodnocení přínosů výzev 80 a 118 OPZ zaměřených na podporu řízení kvality a procesního řízení v organizaci, tvorbu strategických dokumentů, nástroje komunikace s veřejností a realizaci specifických vzdělávacích programů přispívajících ke zkvalitnění rozvoje lidských zdrojů ve veřejné správě. </t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">Předmětem etapy je ověřování přínosu vzdělávacích aktivit realizovaných v rámci projektů pro cílové skupiny, kterými jsou zaměstnanci úřadů samosprávných územních celků a volení zástupci. 
 Data byla ve vztahu ke vzdělávacím aktivitám sbírána od začátku roku 2020. S ohledem na posun v realizaci jednotlivých projektů a vzdělávacích aktivit realizovaných v jejich rámci došlo k posunu sběru dat, který byl ukončen na přelomu let 2021 a 2022. Zpráva z dotazníkového šetření byla zpracována na jaře a v červenci roku 2022. </t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Z výsledků šetření bezprostředně po realizaci kurzu vyplývá, že účastníci vzdělávání byli s realizovanými 
 kurzy nadmíru spokojeni na všech sledovaných úrovních. Vyhovovala jim úroveň lektora, 
@@ -6248,6 +6163,91 @@
 na školení využívá v praxi zhruba polovina respondentů a to nepříliš často.</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Jiná</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>mid-term</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTI2MDYzODkwMDtQcmlsb2hhRE1TO0ZhbHNl</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Zpráva z dotazníkového šetření_080 a 118_účastníci vzdělávání.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>OP PIK</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>01.025.01</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OP PIK  •  Vyhodnocení programu podpory Inovační vouchery OP PIK</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Vyhodnocení programu podpory Inovační vouchery OP PIK</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Vyhodnocení programu podpory Inovační vouchery OP PIK: Vstupní zpráva</t>
+        </is>
+      </c>
+      <c r="F63" s="2">
+        <v>44770</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Předmětem veřejné zakázky je vyhodnocení programu podpory Inovační vouchery OP PIK. Bude zanalyzováno oborové členění podpořených podniků, proveden přehled poskytovatelů služeb podle jejich typů, vyhodnocen vztah mezi příjemcem podpory a poskytovatelem služeb, včetně teritoriálních vazeb a následných společných projektů, v neposlední řadě bude zjištěn podíl projektů s ekonomickými přínosy.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Vstupní evaluační zpráva se zaměřuje na nastavení evaluace programu podpory IV a popisuje předmět evaluace, její cíle, shrnuje jednotlivé evaluační úkoly a evaluační otázky a specifikuje způsob řešení pomocí souhrnné evaluační matice. Tato zpráva rovněž obsahuje detailní popis metodiky evaluace, harmonogram prováděných aktivit a v neposlední řadě také shrnuje hlavní omezení a rizika realizace prováděných evaluačních šetření.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Hlavní zjištění a výsledky budou součástí Závěrečné zprávy této evaluační zakázky.</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>Ano</t>
@@ -6265,53 +6265,58 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Jiná</t>
+          <t>Dopad/výsledky</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>mid-term</t>
+          <t>ad-hoc</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Dopadová/Výsledková</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTI2MDYzODkwMDtQcmlsb2hhRE1TO0ZhbHNl</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTY1NjczMTg3NztQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Zpráva z dotazníkového šetření_080 a 118_účastníci vzdělávání.pdf</t>
+          <t>VIV_CAWI_PP_final.docx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OP PIK</t>
+          <t>PRV</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01.025.01</t>
+          <t>09.005.03</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OP PIK  •  Vyhodnocení programu podpory Inovační vouchery OP PIK</t>
+          <t>PRV  •  Analýza SEA Strategického plánu SZP pro období 2021-2027</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Vyhodnocení programu podpory Inovační vouchery OP PIK</t>
+          <t>Analýza SEA Strategického plánu SZP pro období 2021-2027</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Vyhodnocení programu podpory Inovační vouchery OP PIK: Vstupní zpráva</t>
+          <t>c) Aktualizace vyhodnocení SEA v souvislosti se změnami koncepce SP SZP provedenými objednatelem na základě připomínek Evropské komise</t>
         </is>
       </c>
       <c r="F64" s="2">
-        <v>44770</v>
+        <v>44767</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -6319,195 +6324,105 @@
         </is>
       </c>
       <c r="H64" t="inlineStr">
-        <is>
-          <t>Předmětem veřejné zakázky je vyhodnocení programu podpory Inovační vouchery OP PIK. Bude zanalyzováno oborové členění podpořených podniků, proveden přehled poskytovatelů služeb podle jejich typů, vyhodnocen vztah mezi příjemcem podpory a poskytovatelem služeb, včetně teritoriálních vazeb a následných společných projektů, v neposlední řadě bude zjištěn podíl projektů s ekonomickými přínosy.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Vstupní evaluační zpráva se zaměřuje na nastavení evaluace programu podpory IV a popisuje předmět evaluace, její cíle, shrnuje jednotlivé evaluační úkoly a evaluační otázky a specifikuje způsob řešení pomocí souhrnné evaluační matice. Tato zpráva rovněž obsahuje detailní popis metodiky evaluace, harmonogram prováděných aktivit a v neposlední řadě také shrnuje hlavní omezení a rizika realizace prováděných evaluačních šetření.</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Hlavní zjištění a výsledky budou součástí Závěrečné zprávy této evaluační zakázky.</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Dopad/výsledky</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>ad-hoc</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>Dopadová/Výsledková</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTY1NjczMTg3NztQcmlsb2hhRE1TO0ZhbHNl</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>VIV_CAWI_PP_final.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>PRV</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>09.005.03</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>PRV  •  Analýza SEA Strategického plánu SZP pro období 2021-2027</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Analýza SEA Strategického plánu SZP pro období 2021-2027</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>c) Aktualizace vyhodnocení SEA v souvislosti se změnami koncepce SP SZP provedenými objednatelem na základě připomínek Evropské komise</t>
-        </is>
-      </c>
-      <c r="F65" s="2">
-        <v>44767</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>ukončeno</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
         <is>
           <t xml:space="preserve">Zajištění celého procesu posuzování vlivu Strategického plánu SZP 
 na období 2021-2027 na životní prostředí podle zákona č. 100/2001 Sb., o posuzování vlivů na životní prostředí a o změně některých souvisejících zákonů (zákon o posuzování vlivů na životní prostředí), ve znění pozdějších předpisů.
 </t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">Aktualizace vyhodnocení SEA v souvislosti se změnami koncepce SP SZP provedenými objednatelem na základě připomínek Evropské komise. </t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>viz zpráva</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>Ano</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>Dopad/výsledky</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>ad-hoc</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>Strategická, Tematická, Dopadová/Výsledková</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7MTY4MzI4NTAxMztQcmlsb2hhRE1TO0ZhbHNl</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>SEA SP SZP_výstupy k dílčímu plnění C.zip</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>OP TP</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>08.008.01</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>OP TP  •  Hodnocení evaluační činnosti a příprava podkladů k Průběžné evaluaci pro období 2021-2027</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Hodnocení evaluační činnosti a příprava podkladů k Průběžné evaluaci pro období 2021-2027</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Hodnocení evaluační činnosti a příprava podkladů k Průběžné evaluaci pro období 2021-2027</t>
         </is>
       </c>
-      <c r="F66" s="2">
+      <c r="F65" s="2">
         <v>44764</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>ukončeno</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>Evaluace si klade dva cíle:
 Prvním cílem je zvýšit kvalitu výstupů evaluací realizovaných ŘO OPTP, případně definovat oblasti, kde je prostor pro zlepšení, dále získat doporučení ohledně vhodného nastavení procesů tkajících se evaluační činnosti EJ OPTP: zejména v kontextu komunikace, definování a schvalování záměru evaluace případně dalších analytických činností, komunikace/prezentování závěrů a doporučení. Dále pak má evaluace případně upozornit např. na oblasti, na které je třeba se zaměřit v rámci vzdělávání v tématu evaluací.
 Druhým cílem evaluace bude vypracování podkladů pro nastavení Průběžné evaluaci naplňování cílů OPTP pro období 2021-2027, zejména dotazníkového šetření. Průběžná evaluace by v programovém období 2021-2027 měla sloužit k sledování cílů OPTP.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">Evaluace si klade dva cíle:
 Prvním cílem je vypracování podkladů pro nastavení Průběžné evaluaci naplňování cílů OPTP pro období 2021-2027, zejména dotazníkového šetření. Průběžná evaluace by v programovém období 2021-2027 měla sloužit k sledování cílů OPTP.  
@@ -6515,7 +6430,7 @@
 </t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>1. NASTAVENÍ PRŮBĚŽNÉ EVALUACE A VZTAHU S DODAVATELEM
 Pro zajištění kvalitních a komplexních výstupů shrnujících implementaci celého operačního programu v období 21+ bude klíčové nastavení průběžné evaluace na celou dobu programového období. Průběžná evaluace by měla propojovat kvantitativní (dotazníkové šetření, sběr statistických dat) a kvalitativní (hloubkové rozhovory) metody sběru dat. Důležité bude také nastavit vztah s dodavatelem průběžné evaluace a formát výstupů.  Interní evaluátor bude v tomto kontextu koordinátor, který zprostředkovává informace mezi evaluátory a klienty, a který zajišťuje přístupnost výsledků evaluací výběrem vhodných způsobů prezentace a komunikačních kanálů. 
@@ -6526,6 +6441,96 @@
 Toto budování kontaktů může zkvalitnit získávání informací, které jsou v jiných evaluačních jednotkách získávány prostřednictvím interních evaluací. Ty nejsou vzhledem k velikosti evaluační jednotky možné realizovat, je ovšem možné zapojit evaluátora například přípravou rešerší a shrnutí poznatků získaných z terénního šetření apod.</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Jiná</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>metaevaluace</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>on-going</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Operativní/procesní, Autoevaluace</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODAyMjc4NDk7UHJpbG9oYURNUztGYWxzZQ==</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>Vstupní zpráva_final_7.4.2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>OP ZP</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>05.006.01</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>OP ZP  •  Provedení hodnocení vlivu OPŽP na životní prostředí v období 2021-2027 (SEA)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Provedení hodnocení vlivu OPŽP na životní prostředí v období 2021-2027 (SEA)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Provedení hodnocení vlivu OPŽP na životní prostředí v období 2021-2027 (SEA)</t>
+        </is>
+      </c>
+      <c r="F66" s="2">
+        <v>44760</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ukončeno</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Cílem projektu je provedení posouzení vlivu OPŽP 2021-2027 na životní prostředí v souladu s platnými právními předpisy.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Cílem projektu je provedení posouzení vlivu OPŽP 2021-2027 na životní prostředí v souladu s platnými právními předpisy.</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
           <t>Ano</t>
@@ -6548,27 +6553,27 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>metaevaluace</t>
+          <t>horizontální témata</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>on-going</t>
+          <t>ad-hoc</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Operativní/procesní, Autoevaluace</t>
+          <t>Strategická, Tematická</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODAyMjc4NDk7UHJpbG9oYURNUztGYWxzZQ==</t>
+          <t>https://msiu.mssf.cz/Document.aspx?docID=VU1TUHJpbG9oeUV2YWw7ODgwMjUyMzAxO1ByaWxvaGFETVM7RmFsc2U=</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Vstupní zpráva_final_7.4.2022.pdf</t>
+          <t>Vyhodnocení SEA OPŽP 03082021.pdf</t>
         </is>
       </c>
     </row>
